--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/InvestmentDealInfo.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/InvestmentDealInfo.xlsx
@@ -1,70 +1,76 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="153222"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7755"/>
+    <workbookView windowWidth="19815" windowHeight="7860"/>
   </bookViews>
   <sheets>
     <sheet name="投资交易信息" sheetId="1" r:id="rId1"/>
     <sheet name="CHB_INVEST_TRADE_ENUM" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="211">
   <si>
     <t>操作类型</t>
   </si>
   <si>
+    <t>产品代码</t>
+  </si>
+  <si>
+    <t>行内资产/负债编码</t>
+  </si>
+  <si>
     <t>行内交易编码</t>
   </si>
   <si>
-    <t>产品代码</t>
-  </si>
-  <si>
-    <t>行内资产/负债编码</t>
+    <t>资金流动类型</t>
+  </si>
+  <si>
+    <t>资金流动类型说明</t>
+  </si>
+  <si>
+    <t>数量</t>
+  </si>
+  <si>
+    <t>资产计量方式</t>
   </si>
   <si>
     <t>币种</t>
   </si>
   <si>
+    <t>折算人民币金额</t>
+  </si>
+  <si>
     <t>发生金额</t>
   </si>
   <si>
-    <t>折算人民币金额</t>
-  </si>
-  <si>
-    <t>数量</t>
-  </si>
-  <si>
-    <t>资金流动类型</t>
-  </si>
-  <si>
-    <t>资金流动类型说明</t>
+    <t>单位成交价格（净价）</t>
+  </si>
+  <si>
+    <t>单位成交价格（全价）</t>
+  </si>
+  <si>
+    <t>到期收益率</t>
+  </si>
+  <si>
+    <t>交易对手</t>
+  </si>
+  <si>
+    <t>交易对手方类型</t>
+  </si>
+  <si>
+    <t>成交编号/合同号</t>
   </si>
   <si>
     <t>交易日</t>
   </si>
   <si>
-    <t>交易对手</t>
-  </si>
-  <si>
-    <t>单位成交价格（全价）</t>
-  </si>
-  <si>
-    <t>单位成交价格（净价）</t>
-  </si>
-  <si>
-    <t>到期收益率</t>
-  </si>
-  <si>
-    <t>成交编号/合同号</t>
-  </si>
-  <si>
     <t>备注</t>
   </si>
   <si>
@@ -104,50 +110,911 @@
     <t>12 其他支出</t>
   </si>
   <si>
-    <t>资产计量方式</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>01 公允价值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>02摊余成本</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>交易对手方类型</t>
+  </si>
+  <si>
+    <t>02 摊余成本</t>
+  </si>
+  <si>
+    <t>CNY 人民币</t>
+  </si>
+  <si>
+    <t>HKD 港元</t>
+  </si>
+  <si>
+    <t>USD 美元</t>
+  </si>
+  <si>
+    <t>EUR 欧元</t>
+  </si>
+  <si>
+    <t>JPY 日元</t>
+  </si>
+  <si>
+    <t>MOP 澳门元</t>
+  </si>
+  <si>
+    <t>CHF 瑞士法郎</t>
+  </si>
+  <si>
+    <t>GBP 英镑</t>
+  </si>
+  <si>
+    <t>RUB 俄罗斯卢布</t>
+  </si>
+  <si>
+    <t>CAD 加拿大元</t>
+  </si>
+  <si>
+    <t>DKK 丹麦克朗</t>
+  </si>
+  <si>
+    <t>AUD 澳大利亚元</t>
+  </si>
+  <si>
+    <t>SEK 瑞典克朗</t>
+  </si>
+  <si>
+    <t>SGD 新加坡元</t>
+  </si>
+  <si>
+    <t>TWD 新台币</t>
+  </si>
+  <si>
+    <t>AED 阿拉伯联合酋长国迪尔汗</t>
+  </si>
+  <si>
+    <t>AFN 阿富汗阿富汗尼</t>
+  </si>
+  <si>
+    <t>ALL 阿尔巴尼亚列克</t>
+  </si>
+  <si>
+    <t>AMD 亚美尼亚德拉姆</t>
+  </si>
+  <si>
+    <t>ANG 荷属安的列斯盾</t>
+  </si>
+  <si>
+    <t>AOA 安哥拉宽扎</t>
+  </si>
+  <si>
+    <t>ARS 阿根廷比索</t>
+  </si>
+  <si>
+    <t>AWG 阿鲁巴弗罗林</t>
+  </si>
+  <si>
+    <t>AZN 阿塞拜疆马纳特</t>
+  </si>
+  <si>
+    <t>BAM 波斯尼亚和黑塞哥维那可兑换马克</t>
+  </si>
+  <si>
+    <t>BBD 巴巴多斯元</t>
+  </si>
+  <si>
+    <t>BDT 孟加拉塔卡</t>
+  </si>
+  <si>
+    <t>BGN 保加利亚列弗</t>
+  </si>
+  <si>
+    <t>BHD 巴林第纳尔</t>
+  </si>
+  <si>
+    <t>BIF 布隆迪法郎</t>
+  </si>
+  <si>
+    <t>BMD 百慕大元</t>
+  </si>
+  <si>
+    <t>BND 文莱元</t>
+  </si>
+  <si>
+    <t>BOB 玻利维亚诺</t>
+  </si>
+  <si>
+    <t>BOV 玻利维亚Mvdol基金</t>
+  </si>
+  <si>
+    <t>BRL 巴西雷亚尔</t>
+  </si>
+  <si>
+    <t>BSD 巴哈马元</t>
+  </si>
+  <si>
+    <t>BTN 不丹努扎姆</t>
+  </si>
+  <si>
+    <t>BWP 博茨瓦纳普拉</t>
+  </si>
+  <si>
+    <t>BYR 白俄罗斯卢布</t>
+  </si>
+  <si>
+    <t>BZD 伯利兹元</t>
+  </si>
+  <si>
+    <t>CDF 刚果民主共和国刚果法郎</t>
+  </si>
+  <si>
+    <t>CHE WIR欧元</t>
+  </si>
+  <si>
+    <t>CHW WIR法郎</t>
+  </si>
+  <si>
+    <t>CLF 智利UF基金</t>
+  </si>
+  <si>
+    <t>CLP 智利比索</t>
+  </si>
+  <si>
+    <t>COP 哥伦比亚比索</t>
+  </si>
+  <si>
+    <t>COU 哥伦比亚UVR基金</t>
+  </si>
+  <si>
+    <t>CRC 哥斯达黎加科朗</t>
+  </si>
+  <si>
+    <t>CUC 古巴可兑换比索</t>
+  </si>
+  <si>
+    <t>CUP 古巴比索</t>
+  </si>
+  <si>
+    <t>CVE 佛得角埃斯库多</t>
+  </si>
+  <si>
+    <t>CZK 捷克克朗</t>
+  </si>
+  <si>
+    <t>DJF 吉布提法郎</t>
+  </si>
+  <si>
+    <t>DOP 多米尼加比索</t>
+  </si>
+  <si>
+    <t>DZD 阿尔及利亚第纳尔</t>
+  </si>
+  <si>
+    <t>EGP 埃及镑</t>
+  </si>
+  <si>
+    <t>ERN 厄立特里亚纳克法</t>
+  </si>
+  <si>
+    <t>ETB 埃塞俄比亚比尔</t>
+  </si>
+  <si>
+    <t>FJD 斐济元</t>
+  </si>
+  <si>
+    <t>FKP 福克兰镑</t>
+  </si>
+  <si>
+    <t>GEL 格鲁吉亚拉里</t>
+  </si>
+  <si>
+    <t>GHS 加纳塞地</t>
+  </si>
+  <si>
+    <t>GIP 直布罗陀镑</t>
+  </si>
+  <si>
+    <t>GMD 冈比亚达拉西</t>
+  </si>
+  <si>
+    <t>GNF 几内亚法郎</t>
+  </si>
+  <si>
+    <t>GTQ 危地马拉格查尔</t>
+  </si>
+  <si>
+    <t>GYD 圭亚那元</t>
+  </si>
+  <si>
+    <t>HNL 洪都拉斯伦皮拉</t>
+  </si>
+  <si>
+    <t>HRK 克罗地亚库纳</t>
+  </si>
+  <si>
+    <t>HTG 海地古德</t>
+  </si>
+  <si>
+    <t>HUF 匈牙利福林</t>
+  </si>
+  <si>
+    <t>IDR 印度尼西亚卢比</t>
+  </si>
+  <si>
+    <t>ILS 以色列新谢克尔</t>
+  </si>
+  <si>
+    <t>INR 印度卢比</t>
+  </si>
+  <si>
+    <t>IQD 伊拉克第纳尔</t>
+  </si>
+  <si>
+    <t>IRR 伊朗里亚尔</t>
+  </si>
+  <si>
+    <t>ISK 冰岛克朗</t>
+  </si>
+  <si>
+    <t>JMD 牙买加元</t>
+  </si>
+  <si>
+    <t>JOD 约旦第纳尔</t>
+  </si>
+  <si>
+    <t>KES 肯尼亚先令</t>
+  </si>
+  <si>
+    <t>KGS 吉尔吉斯斯坦索姆</t>
+  </si>
+  <si>
+    <t>KHR 柬埔寨瑞尔</t>
+  </si>
+  <si>
+    <t>KMF 科摩罗法郎</t>
+  </si>
+  <si>
+    <t>KPW 朝鲜元</t>
+  </si>
+  <si>
+    <t>KRW 韩元</t>
+  </si>
+  <si>
+    <t>KWD 科威特第纳尔</t>
+  </si>
+  <si>
+    <t>KYD 开曼群岛元</t>
+  </si>
+  <si>
+    <t>KZT 哈萨克斯坦坚戈</t>
+  </si>
+  <si>
+    <t>LAK 老挝基普</t>
+  </si>
+  <si>
+    <t>LBP 黎巴嫩镑</t>
+  </si>
+  <si>
+    <t>LKR 斯里兰卡卢比</t>
+  </si>
+  <si>
+    <t>LRD 利比里亚元</t>
+  </si>
+  <si>
+    <t>LSL 莱索托洛蒂</t>
+  </si>
+  <si>
+    <t>LYD 利比亚第纳尔</t>
+  </si>
+  <si>
+    <t>MAD 摩洛哥迪拉姆</t>
+  </si>
+  <si>
+    <t>MDL 摩尔多瓦列伊</t>
+  </si>
+  <si>
+    <t>MGA 马达加斯加阿里亚里</t>
+  </si>
+  <si>
+    <t>MKD 马其顿代纳尔</t>
+  </si>
+  <si>
+    <t>MMK 缅甸元</t>
+  </si>
+  <si>
+    <t>MNT 蒙古图格里克</t>
+  </si>
+  <si>
+    <t>MRO 毛里塔尼亚乌吉亚</t>
+  </si>
+  <si>
+    <t>MUR 毛里求斯卢比</t>
+  </si>
+  <si>
+    <t>MVR 马尔代夫拉菲亚</t>
+  </si>
+  <si>
+    <t>MWK 马拉维克瓦查</t>
+  </si>
+  <si>
+    <t>MXN 墨西哥比索</t>
+  </si>
+  <si>
+    <t>MXV 墨西哥UDI基金</t>
+  </si>
+  <si>
+    <t>MYR 马来西亚令吉</t>
+  </si>
+  <si>
+    <t>MZN 莫桑比克梅蒂卡尔</t>
+  </si>
+  <si>
+    <t>NAD 纳米比亚元</t>
+  </si>
+  <si>
+    <t>NGN 尼日利亚奈拉</t>
+  </si>
+  <si>
+    <t>NIO 尼加拉瓜科多巴</t>
+  </si>
+  <si>
+    <t>NOK 挪威克朗</t>
+  </si>
+  <si>
+    <t>NPR 尼泊尔卢比</t>
+  </si>
+  <si>
+    <t>NZD 新西兰元</t>
+  </si>
+  <si>
+    <t>OMR 阿曼里亚尔</t>
+  </si>
+  <si>
+    <t>PAB 巴拿马巴波亚</t>
+  </si>
+  <si>
+    <t>PEN 秘鲁新索尔</t>
+  </si>
+  <si>
+    <t>PGK 巴布亚新几内亚基那</t>
+  </si>
+  <si>
+    <t>PHP 菲律宾比索</t>
+  </si>
+  <si>
+    <t>PKR 巴基斯坦卢比</t>
+  </si>
+  <si>
+    <t>PLN 波兰兹罗提</t>
+  </si>
+  <si>
+    <t>PYG 巴拉圭瓜拉尼</t>
+  </si>
+  <si>
+    <t>QAR 卡塔尔里亚尔</t>
+  </si>
+  <si>
+    <t>RON 罗马尼亚列伊</t>
+  </si>
+  <si>
+    <t>RSD 塞尔维亚第纳尔</t>
+  </si>
+  <si>
+    <t>RWF 卢旺达法郎</t>
+  </si>
+  <si>
+    <t>SAR 沙特里亚尔</t>
+  </si>
+  <si>
+    <t>SBD 所罗门群岛元</t>
+  </si>
+  <si>
+    <t>SCR 塞舌尔卢比</t>
+  </si>
+  <si>
+    <t>SDG 苏丹镑</t>
+  </si>
+  <si>
+    <t>SHP 圣赫勒拿镑</t>
+  </si>
+  <si>
+    <t>SLL 塞拉利昂利昂</t>
+  </si>
+  <si>
+    <t>SOS 索马里先令</t>
+  </si>
+  <si>
+    <t>SRD 苏里南元</t>
+  </si>
+  <si>
+    <t>SSP 南苏丹镑</t>
+  </si>
+  <si>
+    <t>STD 圣多美和普林西比多布拉</t>
+  </si>
+  <si>
+    <t>SVC 萨尔瓦多科朗</t>
+  </si>
+  <si>
+    <t>SYP 叙利亚镑</t>
+  </si>
+  <si>
+    <t>SZL 斯威士兰里兰吉尼</t>
+  </si>
+  <si>
+    <t>THB 泰铢</t>
+  </si>
+  <si>
+    <t>TJS 塔吉克斯坦索莫尼</t>
+  </si>
+  <si>
+    <t>TMT 土库曼斯坦马纳特</t>
+  </si>
+  <si>
+    <t>TND 突尼斯第纳尔</t>
+  </si>
+  <si>
+    <t>TOP 汤加潘加</t>
+  </si>
+  <si>
+    <t>TRY 土耳其里拉</t>
+  </si>
+  <si>
+    <t>TTD 特立尼达和多巴哥元</t>
+  </si>
+  <si>
+    <t>TZS 坦桑尼亚先令</t>
+  </si>
+  <si>
+    <t>UAH 乌克兰格里夫尼亚</t>
+  </si>
+  <si>
+    <t>UGX 乌干达先令</t>
+  </si>
+  <si>
+    <t>USN 美元翌日基金</t>
+  </si>
+  <si>
+    <t>UYI 乌拉圭URUIURUI基金</t>
+  </si>
+  <si>
+    <t>UYU 乌拉圭比索</t>
+  </si>
+  <si>
+    <t>UZS 乌兹别克斯坦苏姆</t>
+  </si>
+  <si>
+    <t>VEF 委内瑞拉博利瓦</t>
+  </si>
+  <si>
+    <t>VND 越南盾</t>
+  </si>
+  <si>
+    <t>VUV 瓦努阿图瓦图</t>
+  </si>
+  <si>
+    <t>WST 萨摩亚塔拉</t>
+  </si>
+  <si>
+    <t>XAF 中非金融合作法郎（中非法郎）</t>
+  </si>
+  <si>
+    <t>XAG 银（一盎司）</t>
+  </si>
+  <si>
+    <t>XAU 金（一盎司）</t>
+  </si>
+  <si>
+    <t>XBA 欧洲混合单位（债券市场单位）</t>
+  </si>
+  <si>
+    <t>XBB 欧洲货币单位（债券市场单位）</t>
+  </si>
+  <si>
+    <t>XBC 欧洲计算单位9（债券市场单位）</t>
+  </si>
+  <si>
+    <t>XBD 欧洲计算单位17（债券市场单位）</t>
+  </si>
+  <si>
+    <t>XCD 东加勒比元</t>
+  </si>
+  <si>
+    <t>XDR 特别提款权（国际货币基金）</t>
+  </si>
+  <si>
+    <t>XOF 非洲金融共同体法郎（西非法郎）</t>
+  </si>
+  <si>
+    <t>XPD 钯（一盎司）</t>
+  </si>
+  <si>
+    <t>XPF 太平洋法兰西共同体法郎（CFP法郎）</t>
+  </si>
+  <si>
+    <t>XPT 铂（一盎司）</t>
+  </si>
+  <si>
+    <t>XSU 厄瓜多尔苏克雷</t>
+  </si>
+  <si>
+    <t>XTS 为测试保留的代码</t>
+  </si>
+  <si>
+    <t>XUA 非洲开发银行账户单位</t>
+  </si>
+  <si>
+    <t>XXX 非货币交易单位</t>
+  </si>
+  <si>
+    <t>YER 也门里亚尔</t>
+  </si>
+  <si>
+    <t>ZAR 南非兰特</t>
+  </si>
+  <si>
+    <t>ZMW 赞比亚克瓦查</t>
+  </si>
+  <si>
+    <t>ZWL 津巴布韦元</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="宋体"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -155,9 +1022,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -166,17 +1275,61 @@
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
+    <cellStyle name="输入" xfId="3" builtinId="20"/>
+    <cellStyle name="货币" xfId="4" builtinId="4"/>
+    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
+    <cellStyle name="差" xfId="7" builtinId="27"/>
+    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
+    <cellStyle name="超链接" xfId="10" builtinId="8"/>
+    <cellStyle name="百分比" xfId="11" builtinId="5"/>
+    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
+    <cellStyle name="注释" xfId="13" builtinId="10"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
+    <cellStyle name="标题" xfId="17" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
+    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
+    <cellStyle name="输出" xfId="24" builtinId="21"/>
+    <cellStyle name="计算" xfId="25" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
+    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
+    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
+    <cellStyle name="汇总" xfId="30" builtinId="25"/>
+    <cellStyle name="好" xfId="31" builtinId="26"/>
+    <cellStyle name="适中" xfId="32" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
+    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
+    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
+    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
+    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -225,7 +1378,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -260,7 +1413,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -434,193 +1587,710 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:S2"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="2" width="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="18.375" customWidth="1"/>
     <col min="4" max="4" width="15" customWidth="1"/>
-    <col min="5" max="5" width="18" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="24" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="24" customWidth="1"/>
     <col min="7" max="8" width="12.125" customWidth="1"/>
-    <col min="9" max="9" width="10" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="21.375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="21" customWidth="1"/>
+    <col min="11" max="11" width="12" customWidth="1"/>
+    <col min="12" max="13" width="21.375" customWidth="1"/>
+    <col min="14" max="14" width="15" customWidth="1"/>
     <col min="15" max="15" width="14.25" customWidth="1"/>
     <col min="16" max="16" width="18" customWidth="1"/>
-    <col min="17" max="17" width="22" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="22" customWidth="1"/>
+    <col min="18" max="18" width="10" customWidth="1"/>
     <col min="19" max="19" width="13.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="31.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" ht="31.35" customHeight="1" spans="1:19">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
       <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="F1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="G1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I1" t="s">
-        <v>4</v>
-      </c>
-      <c r="J1" t="s">
-        <v>6</v>
-      </c>
       <c r="K1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="M1" t="s">
         <v>12</v>
       </c>
       <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="O1" t="s">
-        <v>11</v>
-      </c>
       <c r="P1" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="Q1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R1" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="S1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="24.95" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="2" ht="24.95" customHeight="1"/>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <dataValidations count="2">
+  <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="A2:A1048576">
       <formula1>"导出,新增,修改,删除"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="E2:E1048576">
+      <formula1>CHB_INVEST_TRADE_ENUM!$A$3:$L$3</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H1048576">
+      <formula1>CHB_INVEST_TRADE_ENUM!$A$5:$B$5</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I1048576">
+      <formula1>CHB_INVEST_TRADE_ENUM!$A$7:$FV$7</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P1048576">
       <formula1>"01 住户,02 广义政府,03 非金融企业,04 银行业存款类金融机构,05 银行非存款类金融机构,06 非银行业金融机构,07银行非保本理财,08 信托公司资管产品,09 证券公司及其子公司资管产品,10 基金管理公司及其子公司专户,11 期货公司及其子公司资管产品,12 保险资管产品,13 金融资产投资公司资管产品,14 公募基金,15 私募基金,16 其他特定目的载体,17 境外,99 其他"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1">
-          <x14:formula1>
-            <xm:f>CHB_INVEST_TRADE_ENUM!$A$3:$L$3</xm:f>
-          </x14:formula1>
-          <xm:sqref>E2:E1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1">
-          <x14:formula1>
-            <xm:f>CHB_INVEST_TRADE_ENUM!#REF!</xm:f>
-          </x14:formula1>
-          <xm:sqref>I2:I1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>CHB_INVEST_TRADE_ENUM!$A$5:$B$5</xm:f>
-          </x14:formula1>
-          <xm:sqref>H2:H1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A3:L5"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A3:FV7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6"/>
   <cols>
-    <col min="1" max="1" width="13.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.375" customWidth="1"/>
+    <col min="2" max="2" width="18.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" ht="24.95" customHeight="1" spans="1:12">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B5" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:178">
+      <c r="A7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7" t="s">
+        <v>39</v>
+      </c>
+      <c r="H7" t="s">
+        <v>40</v>
+      </c>
+      <c r="I7" t="s">
+        <v>41</v>
+      </c>
+      <c r="J7" t="s">
+        <v>42</v>
+      </c>
+      <c r="K7" t="s">
+        <v>43</v>
+      </c>
+      <c r="L7" t="s">
+        <v>44</v>
+      </c>
+      <c r="M7" t="s">
+        <v>45</v>
+      </c>
+      <c r="N7" t="s">
+        <v>46</v>
+      </c>
+      <c r="O7" t="s">
+        <v>47</v>
+      </c>
+      <c r="P7" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>49</v>
+      </c>
+      <c r="R7" t="s">
+        <v>50</v>
+      </c>
+      <c r="S7" t="s">
+        <v>51</v>
+      </c>
+      <c r="T7" t="s">
+        <v>52</v>
+      </c>
+      <c r="U7" t="s">
+        <v>53</v>
+      </c>
+      <c r="V7" t="s">
+        <v>54</v>
+      </c>
+      <c r="W7" t="s">
+        <v>55</v>
+      </c>
+      <c r="X7" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>59</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>60</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>62</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>63</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>64</v>
+      </c>
+      <c r="AG7" t="s">
+        <v>65</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>66</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ7" t="s">
+        <v>68</v>
+      </c>
+      <c r="AK7" t="s">
+        <v>69</v>
+      </c>
+      <c r="AL7" t="s">
+        <v>70</v>
+      </c>
+      <c r="AM7" t="s">
+        <v>71</v>
+      </c>
+      <c r="AN7" t="s">
+        <v>72</v>
+      </c>
+      <c r="AO7" t="s">
+        <v>73</v>
+      </c>
+      <c r="AP7" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ7" t="s">
+        <v>75</v>
+      </c>
+      <c r="AR7" t="s">
+        <v>76</v>
+      </c>
+      <c r="AS7" t="s">
+        <v>77</v>
+      </c>
+      <c r="AT7" t="s">
+        <v>78</v>
+      </c>
+      <c r="AU7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AV7" t="s">
+        <v>80</v>
+      </c>
+      <c r="AW7" t="s">
+        <v>81</v>
+      </c>
+      <c r="AX7" t="s">
+        <v>82</v>
+      </c>
+      <c r="AY7" t="s">
+        <v>83</v>
+      </c>
+      <c r="AZ7" t="s">
+        <v>84</v>
+      </c>
+      <c r="BA7" t="s">
+        <v>85</v>
+      </c>
+      <c r="BB7" t="s">
+        <v>86</v>
+      </c>
+      <c r="BC7" t="s">
+        <v>87</v>
+      </c>
+      <c r="BD7" t="s">
+        <v>88</v>
+      </c>
+      <c r="BE7" t="s">
+        <v>89</v>
+      </c>
+      <c r="BF7" t="s">
+        <v>90</v>
+      </c>
+      <c r="BG7" t="s">
+        <v>91</v>
+      </c>
+      <c r="BH7" t="s">
+        <v>92</v>
+      </c>
+      <c r="BI7" t="s">
+        <v>93</v>
+      </c>
+      <c r="BJ7" t="s">
+        <v>94</v>
+      </c>
+      <c r="BK7" t="s">
+        <v>95</v>
+      </c>
+      <c r="BL7" t="s">
+        <v>96</v>
+      </c>
+      <c r="BM7" t="s">
+        <v>97</v>
+      </c>
+      <c r="BN7" t="s">
+        <v>98</v>
+      </c>
+      <c r="BO7" t="s">
+        <v>99</v>
+      </c>
+      <c r="BP7" t="s">
+        <v>100</v>
+      </c>
+      <c r="BQ7" t="s">
+        <v>101</v>
+      </c>
+      <c r="BR7" t="s">
+        <v>102</v>
+      </c>
+      <c r="BS7" t="s">
+        <v>103</v>
+      </c>
+      <c r="BT7" t="s">
+        <v>104</v>
+      </c>
+      <c r="BU7" t="s">
+        <v>105</v>
+      </c>
+      <c r="BV7" t="s">
+        <v>106</v>
+      </c>
+      <c r="BW7" t="s">
+        <v>107</v>
+      </c>
+      <c r="BX7" t="s">
+        <v>108</v>
+      </c>
+      <c r="BY7" t="s">
+        <v>109</v>
+      </c>
+      <c r="BZ7" t="s">
+        <v>110</v>
+      </c>
+      <c r="CA7" t="s">
+        <v>111</v>
+      </c>
+      <c r="CB7" t="s">
+        <v>112</v>
+      </c>
+      <c r="CC7" t="s">
+        <v>113</v>
+      </c>
+      <c r="CD7" t="s">
+        <v>114</v>
+      </c>
+      <c r="CE7" t="s">
+        <v>115</v>
+      </c>
+      <c r="CF7" t="s">
+        <v>116</v>
+      </c>
+      <c r="CG7" t="s">
+        <v>117</v>
+      </c>
+      <c r="CH7" t="s">
+        <v>118</v>
+      </c>
+      <c r="CI7" t="s">
+        <v>119</v>
+      </c>
+      <c r="CJ7" t="s">
+        <v>120</v>
+      </c>
+      <c r="CK7" t="s">
+        <v>121</v>
+      </c>
+      <c r="CL7" t="s">
+        <v>122</v>
+      </c>
+      <c r="CM7" t="s">
+        <v>123</v>
+      </c>
+      <c r="CN7" t="s">
+        <v>124</v>
+      </c>
+      <c r="CO7" t="s">
+        <v>125</v>
+      </c>
+      <c r="CP7" t="s">
+        <v>126</v>
+      </c>
+      <c r="CQ7" t="s">
+        <v>127</v>
+      </c>
+      <c r="CR7" t="s">
+        <v>128</v>
+      </c>
+      <c r="CS7" t="s">
+        <v>129</v>
+      </c>
+      <c r="CT7" t="s">
+        <v>130</v>
+      </c>
+      <c r="CU7" t="s">
+        <v>131</v>
+      </c>
+      <c r="CV7" t="s">
+        <v>132</v>
+      </c>
+      <c r="CW7" t="s">
+        <v>133</v>
+      </c>
+      <c r="CX7" t="s">
+        <v>134</v>
+      </c>
+      <c r="CY7" t="s">
+        <v>135</v>
+      </c>
+      <c r="CZ7" t="s">
+        <v>136</v>
+      </c>
+      <c r="DA7" t="s">
+        <v>137</v>
+      </c>
+      <c r="DB7" t="s">
+        <v>138</v>
+      </c>
+      <c r="DC7" t="s">
+        <v>139</v>
+      </c>
+      <c r="DD7" t="s">
+        <v>140</v>
+      </c>
+      <c r="DE7" t="s">
+        <v>141</v>
+      </c>
+      <c r="DF7" t="s">
+        <v>142</v>
+      </c>
+      <c r="DG7" t="s">
+        <v>143</v>
+      </c>
+      <c r="DH7" t="s">
+        <v>144</v>
+      </c>
+      <c r="DI7" t="s">
+        <v>145</v>
+      </c>
+      <c r="DJ7" t="s">
+        <v>146</v>
+      </c>
+      <c r="DK7" t="s">
+        <v>147</v>
+      </c>
+      <c r="DL7" t="s">
+        <v>148</v>
+      </c>
+      <c r="DM7" t="s">
+        <v>149</v>
+      </c>
+      <c r="DN7" t="s">
+        <v>150</v>
+      </c>
+      <c r="DO7" t="s">
+        <v>151</v>
+      </c>
+      <c r="DP7" t="s">
+        <v>152</v>
+      </c>
+      <c r="DQ7" t="s">
+        <v>153</v>
+      </c>
+      <c r="DR7" t="s">
+        <v>154</v>
+      </c>
+      <c r="DS7" t="s">
+        <v>155</v>
+      </c>
+      <c r="DT7" t="s">
+        <v>156</v>
+      </c>
+      <c r="DU7" t="s">
+        <v>157</v>
+      </c>
+      <c r="DV7" t="s">
+        <v>158</v>
+      </c>
+      <c r="DW7" t="s">
+        <v>159</v>
+      </c>
+      <c r="DX7" t="s">
+        <v>160</v>
+      </c>
+      <c r="DY7" t="s">
+        <v>161</v>
+      </c>
+      <c r="DZ7" t="s">
+        <v>162</v>
+      </c>
+      <c r="EA7" t="s">
+        <v>163</v>
+      </c>
+      <c r="EB7" t="s">
+        <v>164</v>
+      </c>
+      <c r="EC7" t="s">
+        <v>165</v>
+      </c>
+      <c r="ED7" t="s">
+        <v>166</v>
+      </c>
+      <c r="EE7" t="s">
+        <v>167</v>
+      </c>
+      <c r="EF7" t="s">
+        <v>168</v>
+      </c>
+      <c r="EG7" t="s">
+        <v>169</v>
+      </c>
+      <c r="EH7" t="s">
+        <v>170</v>
+      </c>
+      <c r="EI7" t="s">
+        <v>171</v>
+      </c>
+      <c r="EJ7" t="s">
+        <v>172</v>
+      </c>
+      <c r="EK7" t="s">
+        <v>173</v>
+      </c>
+      <c r="EL7" t="s">
+        <v>174</v>
+      </c>
+      <c r="EM7" t="s">
+        <v>175</v>
+      </c>
+      <c r="EN7" t="s">
+        <v>176</v>
+      </c>
+      <c r="EO7" t="s">
+        <v>177</v>
+      </c>
+      <c r="EP7" t="s">
+        <v>178</v>
+      </c>
+      <c r="EQ7" t="s">
+        <v>179</v>
+      </c>
+      <c r="ER7" t="s">
+        <v>180</v>
+      </c>
+      <c r="ES7" t="s">
+        <v>181</v>
+      </c>
+      <c r="ET7" t="s">
+        <v>182</v>
+      </c>
+      <c r="EU7" t="s">
+        <v>183</v>
+      </c>
+      <c r="EV7" t="s">
+        <v>184</v>
+      </c>
+      <c r="EW7" t="s">
+        <v>185</v>
+      </c>
+      <c r="EX7" t="s">
+        <v>186</v>
+      </c>
+      <c r="EY7" t="s">
+        <v>187</v>
+      </c>
+      <c r="EZ7" t="s">
+        <v>188</v>
+      </c>
+      <c r="FA7" t="s">
+        <v>189</v>
+      </c>
+      <c r="FB7" t="s">
+        <v>190</v>
+      </c>
+      <c r="FC7" t="s">
+        <v>191</v>
+      </c>
+      <c r="FD7" t="s">
+        <v>192</v>
+      </c>
+      <c r="FE7" t="s">
+        <v>193</v>
+      </c>
+      <c r="FF7" t="s">
+        <v>194</v>
+      </c>
+      <c r="FG7" t="s">
+        <v>195</v>
+      </c>
+      <c r="FH7" t="s">
+        <v>196</v>
+      </c>
+      <c r="FI7" t="s">
+        <v>197</v>
+      </c>
+      <c r="FJ7" t="s">
+        <v>198</v>
+      </c>
+      <c r="FK7" t="s">
+        <v>199</v>
+      </c>
+      <c r="FL7" t="s">
+        <v>200</v>
+      </c>
+      <c r="FM7" t="s">
+        <v>201</v>
+      </c>
+      <c r="FN7" t="s">
+        <v>202</v>
+      </c>
+      <c r="FO7" t="s">
+        <v>203</v>
+      </c>
+      <c r="FP7" t="s">
+        <v>204</v>
+      </c>
+      <c r="FQ7" t="s">
+        <v>205</v>
+      </c>
+      <c r="FR7" t="s">
+        <v>206</v>
+      </c>
+      <c r="FS7" t="s">
+        <v>207</v>
+      </c>
+      <c r="FT7" t="s">
+        <v>208</v>
+      </c>
+      <c r="FU7" t="s">
+        <v>209</v>
+      </c>
+      <c r="FV7" t="s">
+        <v>210</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/InvestmentDealInfo.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/InvestmentDealInfo.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19815" windowHeight="7860"/>
+    <workbookView windowWidth="19815" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="投资交易信息" sheetId="1" r:id="rId1"/>
     <sheet name="CHB_INVEST_TRADE_ENUM" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="144525" concurrentCalc="0"/>
 </workbook>
 </file>
 
@@ -654,11 +654,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -672,13 +673,12 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -698,10 +698,34 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -720,38 +744,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -775,6 +778,14 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
@@ -789,32 +800,22 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -829,7 +830,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -841,37 +938,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -889,19 +968,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -913,31 +980,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -949,67 +1004,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1023,16 +1024,16 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
+      <right style="double">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
+      <top style="double">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
+      <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -1053,11 +1054,32 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1073,6 +1095,15 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -1082,41 +1113,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1125,153 +1126,156 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+  </cellStyleXfs>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-  </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1593,8 +1597,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
+  <dimension ref="A1:S1041"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="18.375" customWidth="1"/>
@@ -1610,7 +1614,7 @@
     <col min="15" max="15" width="14.25" customWidth="1"/>
     <col min="16" max="16" width="18" customWidth="1"/>
     <col min="17" max="17" width="22" customWidth="1"/>
-    <col min="18" max="18" width="10" customWidth="1"/>
+    <col min="18" max="18" width="13.75" customWidth="1"/>
     <col min="19" max="19" width="13.625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1673,23 +1677,3181 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" ht="24.95" customHeight="1"/>
+    <row r="2" ht="24.95" customHeight="1" spans="18:18">
+      <c r="R2" s="1"/>
+    </row>
+    <row r="3" spans="18:18">
+      <c r="R3" s="1"/>
+    </row>
+    <row r="4" spans="18:18">
+      <c r="R4" s="1"/>
+    </row>
+    <row r="5" spans="18:18">
+      <c r="R5" s="1"/>
+    </row>
+    <row r="6" spans="18:18">
+      <c r="R6" s="1"/>
+    </row>
+    <row r="7" spans="18:18">
+      <c r="R7" s="1"/>
+    </row>
+    <row r="8" spans="18:18">
+      <c r="R8" s="1"/>
+    </row>
+    <row r="9" spans="18:18">
+      <c r="R9" s="1"/>
+    </row>
+    <row r="10" spans="18:18">
+      <c r="R10" s="1"/>
+    </row>
+    <row r="11" spans="18:18">
+      <c r="R11" s="1"/>
+    </row>
+    <row r="12" spans="18:18">
+      <c r="R12" s="1"/>
+    </row>
+    <row r="13" spans="18:18">
+      <c r="R13" s="1"/>
+    </row>
+    <row r="14" spans="18:18">
+      <c r="R14" s="1"/>
+    </row>
+    <row r="15" spans="18:18">
+      <c r="R15" s="1"/>
+    </row>
+    <row r="16" spans="18:18">
+      <c r="R16" s="1"/>
+    </row>
+    <row r="17" spans="18:18">
+      <c r="R17" s="1"/>
+    </row>
+    <row r="18" spans="18:18">
+      <c r="R18" s="1"/>
+    </row>
+    <row r="19" spans="18:18">
+      <c r="R19" s="1"/>
+    </row>
+    <row r="20" spans="18:18">
+      <c r="R20" s="1"/>
+    </row>
+    <row r="21" spans="18:18">
+      <c r="R21" s="1"/>
+    </row>
+    <row r="22" spans="18:18">
+      <c r="R22" s="1"/>
+    </row>
+    <row r="23" spans="18:18">
+      <c r="R23" s="1"/>
+    </row>
+    <row r="24" spans="18:18">
+      <c r="R24" s="1"/>
+    </row>
+    <row r="25" spans="18:18">
+      <c r="R25" s="1"/>
+    </row>
+    <row r="26" spans="18:18">
+      <c r="R26" s="1"/>
+    </row>
+    <row r="27" spans="18:18">
+      <c r="R27" s="1"/>
+    </row>
+    <row r="28" spans="18:18">
+      <c r="R28" s="1"/>
+    </row>
+    <row r="29" spans="18:18">
+      <c r="R29" s="1"/>
+    </row>
+    <row r="30" spans="18:18">
+      <c r="R30" s="1"/>
+    </row>
+    <row r="31" spans="18:18">
+      <c r="R31" s="1"/>
+    </row>
+    <row r="32" spans="18:18">
+      <c r="R32" s="1"/>
+    </row>
+    <row r="33" spans="18:18">
+      <c r="R33" s="1"/>
+    </row>
+    <row r="34" spans="18:18">
+      <c r="R34" s="1"/>
+    </row>
+    <row r="35" spans="18:18">
+      <c r="R35" s="1"/>
+    </row>
+    <row r="36" spans="18:18">
+      <c r="R36" s="1"/>
+    </row>
+    <row r="37" spans="18:18">
+      <c r="R37" s="1"/>
+    </row>
+    <row r="38" spans="18:18">
+      <c r="R38" s="1"/>
+    </row>
+    <row r="39" spans="18:18">
+      <c r="R39" s="1"/>
+    </row>
+    <row r="40" spans="18:18">
+      <c r="R40" s="1"/>
+    </row>
+    <row r="41" spans="18:18">
+      <c r="R41" s="1"/>
+    </row>
+    <row r="42" spans="18:18">
+      <c r="R42" s="1"/>
+    </row>
+    <row r="43" spans="18:18">
+      <c r="R43" s="1"/>
+    </row>
+    <row r="44" spans="18:18">
+      <c r="R44" s="1"/>
+    </row>
+    <row r="45" spans="18:18">
+      <c r="R45" s="1"/>
+    </row>
+    <row r="46" spans="18:18">
+      <c r="R46" s="1"/>
+    </row>
+    <row r="47" spans="18:18">
+      <c r="R47" s="1"/>
+    </row>
+    <row r="48" spans="18:18">
+      <c r="R48" s="1"/>
+    </row>
+    <row r="49" spans="18:18">
+      <c r="R49" s="1"/>
+    </row>
+    <row r="50" spans="18:18">
+      <c r="R50" s="1"/>
+    </row>
+    <row r="51" spans="18:18">
+      <c r="R51" s="1"/>
+    </row>
+    <row r="52" spans="18:18">
+      <c r="R52" s="1"/>
+    </row>
+    <row r="53" spans="18:18">
+      <c r="R53" s="1"/>
+    </row>
+    <row r="54" spans="18:18">
+      <c r="R54" s="1"/>
+    </row>
+    <row r="55" spans="18:18">
+      <c r="R55" s="1"/>
+    </row>
+    <row r="56" spans="18:18">
+      <c r="R56" s="1"/>
+    </row>
+    <row r="57" spans="18:18">
+      <c r="R57" s="1"/>
+    </row>
+    <row r="58" spans="18:18">
+      <c r="R58" s="1"/>
+    </row>
+    <row r="59" spans="18:18">
+      <c r="R59" s="1"/>
+    </row>
+    <row r="60" spans="18:18">
+      <c r="R60" s="1"/>
+    </row>
+    <row r="61" spans="18:18">
+      <c r="R61" s="1"/>
+    </row>
+    <row r="62" spans="18:18">
+      <c r="R62" s="1"/>
+    </row>
+    <row r="63" spans="18:18">
+      <c r="R63" s="1"/>
+    </row>
+    <row r="64" spans="18:18">
+      <c r="R64" s="1"/>
+    </row>
+    <row r="65" spans="18:18">
+      <c r="R65" s="1"/>
+    </row>
+    <row r="66" spans="18:18">
+      <c r="R66" s="1"/>
+    </row>
+    <row r="67" spans="18:18">
+      <c r="R67" s="1"/>
+    </row>
+    <row r="68" spans="18:18">
+      <c r="R68" s="1"/>
+    </row>
+    <row r="69" spans="18:18">
+      <c r="R69" s="1"/>
+    </row>
+    <row r="70" spans="18:18">
+      <c r="R70" s="1"/>
+    </row>
+    <row r="71" spans="18:18">
+      <c r="R71" s="1"/>
+    </row>
+    <row r="72" spans="18:18">
+      <c r="R72" s="1"/>
+    </row>
+    <row r="73" spans="18:18">
+      <c r="R73" s="1"/>
+    </row>
+    <row r="74" spans="18:18">
+      <c r="R74" s="1"/>
+    </row>
+    <row r="75" spans="18:18">
+      <c r="R75" s="1"/>
+    </row>
+    <row r="76" spans="18:18">
+      <c r="R76" s="1"/>
+    </row>
+    <row r="77" spans="18:18">
+      <c r="R77" s="1"/>
+    </row>
+    <row r="78" spans="18:18">
+      <c r="R78" s="1"/>
+    </row>
+    <row r="79" spans="18:18">
+      <c r="R79" s="1"/>
+    </row>
+    <row r="80" spans="18:18">
+      <c r="R80" s="1"/>
+    </row>
+    <row r="81" spans="18:18">
+      <c r="R81" s="1"/>
+    </row>
+    <row r="82" spans="18:18">
+      <c r="R82" s="1"/>
+    </row>
+    <row r="83" spans="18:18">
+      <c r="R83" s="1"/>
+    </row>
+    <row r="84" spans="18:18">
+      <c r="R84" s="1"/>
+    </row>
+    <row r="85" spans="18:18">
+      <c r="R85" s="1"/>
+    </row>
+    <row r="86" spans="18:18">
+      <c r="R86" s="1"/>
+    </row>
+    <row r="87" spans="18:18">
+      <c r="R87" s="1"/>
+    </row>
+    <row r="88" spans="18:18">
+      <c r="R88" s="1"/>
+    </row>
+    <row r="89" spans="18:18">
+      <c r="R89" s="1"/>
+    </row>
+    <row r="90" spans="18:18">
+      <c r="R90" s="1"/>
+    </row>
+    <row r="91" spans="18:18">
+      <c r="R91" s="1"/>
+    </row>
+    <row r="92" spans="18:18">
+      <c r="R92" s="1"/>
+    </row>
+    <row r="93" spans="18:18">
+      <c r="R93" s="1"/>
+    </row>
+    <row r="94" spans="18:18">
+      <c r="R94" s="1"/>
+    </row>
+    <row r="95" spans="18:18">
+      <c r="R95" s="1"/>
+    </row>
+    <row r="96" spans="18:18">
+      <c r="R96" s="1"/>
+    </row>
+    <row r="97" spans="18:18">
+      <c r="R97" s="1"/>
+    </row>
+    <row r="98" spans="18:18">
+      <c r="R98" s="1"/>
+    </row>
+    <row r="99" spans="18:18">
+      <c r="R99" s="1"/>
+    </row>
+    <row r="100" spans="18:18">
+      <c r="R100" s="1"/>
+    </row>
+    <row r="101" spans="18:18">
+      <c r="R101" s="1"/>
+    </row>
+    <row r="102" spans="18:18">
+      <c r="R102" s="1"/>
+    </row>
+    <row r="103" spans="18:18">
+      <c r="R103" s="1"/>
+    </row>
+    <row r="104" spans="18:18">
+      <c r="R104" s="1"/>
+    </row>
+    <row r="105" spans="18:18">
+      <c r="R105" s="1"/>
+    </row>
+    <row r="106" spans="18:18">
+      <c r="R106" s="1"/>
+    </row>
+    <row r="107" spans="18:18">
+      <c r="R107" s="1"/>
+    </row>
+    <row r="108" spans="18:18">
+      <c r="R108" s="1"/>
+    </row>
+    <row r="109" spans="18:18">
+      <c r="R109" s="1"/>
+    </row>
+    <row r="110" spans="18:18">
+      <c r="R110" s="1"/>
+    </row>
+    <row r="111" spans="18:18">
+      <c r="R111" s="1"/>
+    </row>
+    <row r="112" spans="18:18">
+      <c r="R112" s="1"/>
+    </row>
+    <row r="113" spans="18:18">
+      <c r="R113" s="1"/>
+    </row>
+    <row r="114" spans="18:18">
+      <c r="R114" s="1"/>
+    </row>
+    <row r="115" spans="18:18">
+      <c r="R115" s="1"/>
+    </row>
+    <row r="116" spans="18:18">
+      <c r="R116" s="1"/>
+    </row>
+    <row r="117" spans="18:18">
+      <c r="R117" s="1"/>
+    </row>
+    <row r="118" spans="18:18">
+      <c r="R118" s="1"/>
+    </row>
+    <row r="119" spans="18:18">
+      <c r="R119" s="1"/>
+    </row>
+    <row r="120" spans="18:18">
+      <c r="R120" s="1"/>
+    </row>
+    <row r="121" spans="18:18">
+      <c r="R121" s="1"/>
+    </row>
+    <row r="122" spans="18:18">
+      <c r="R122" s="1"/>
+    </row>
+    <row r="123" spans="18:18">
+      <c r="R123" s="1"/>
+    </row>
+    <row r="124" spans="18:18">
+      <c r="R124" s="1"/>
+    </row>
+    <row r="125" spans="18:18">
+      <c r="R125" s="1"/>
+    </row>
+    <row r="126" spans="18:18">
+      <c r="R126" s="1"/>
+    </row>
+    <row r="127" spans="18:18">
+      <c r="R127" s="1"/>
+    </row>
+    <row r="128" spans="18:18">
+      <c r="R128" s="1"/>
+    </row>
+    <row r="129" spans="18:18">
+      <c r="R129" s="1"/>
+    </row>
+    <row r="130" spans="18:18">
+      <c r="R130" s="1"/>
+    </row>
+    <row r="131" spans="18:18">
+      <c r="R131" s="1"/>
+    </row>
+    <row r="132" spans="18:18">
+      <c r="R132" s="1"/>
+    </row>
+    <row r="133" spans="18:18">
+      <c r="R133" s="1"/>
+    </row>
+    <row r="134" spans="18:18">
+      <c r="R134" s="1"/>
+    </row>
+    <row r="135" spans="18:18">
+      <c r="R135" s="1"/>
+    </row>
+    <row r="136" spans="18:18">
+      <c r="R136" s="1"/>
+    </row>
+    <row r="137" spans="18:18">
+      <c r="R137" s="1"/>
+    </row>
+    <row r="138" spans="18:18">
+      <c r="R138" s="1"/>
+    </row>
+    <row r="139" spans="18:18">
+      <c r="R139" s="1"/>
+    </row>
+    <row r="140" spans="18:18">
+      <c r="R140" s="1"/>
+    </row>
+    <row r="141" spans="18:18">
+      <c r="R141" s="1"/>
+    </row>
+    <row r="142" spans="18:18">
+      <c r="R142" s="1"/>
+    </row>
+    <row r="143" spans="18:18">
+      <c r="R143" s="1"/>
+    </row>
+    <row r="144" spans="18:18">
+      <c r="R144" s="1"/>
+    </row>
+    <row r="145" spans="18:18">
+      <c r="R145" s="1"/>
+    </row>
+    <row r="146" spans="18:18">
+      <c r="R146" s="1"/>
+    </row>
+    <row r="147" spans="18:18">
+      <c r="R147" s="1"/>
+    </row>
+    <row r="148" spans="18:18">
+      <c r="R148" s="1"/>
+    </row>
+    <row r="149" spans="18:18">
+      <c r="R149" s="1"/>
+    </row>
+    <row r="150" spans="18:18">
+      <c r="R150" s="1"/>
+    </row>
+    <row r="151" spans="18:18">
+      <c r="R151" s="1"/>
+    </row>
+    <row r="152" spans="18:18">
+      <c r="R152" s="1"/>
+    </row>
+    <row r="153" spans="18:18">
+      <c r="R153" s="1"/>
+    </row>
+    <row r="154" spans="18:18">
+      <c r="R154" s="1"/>
+    </row>
+    <row r="155" spans="18:18">
+      <c r="R155" s="1"/>
+    </row>
+    <row r="156" spans="18:18">
+      <c r="R156" s="1"/>
+    </row>
+    <row r="157" spans="18:18">
+      <c r="R157" s="1"/>
+    </row>
+    <row r="158" spans="18:18">
+      <c r="R158" s="1"/>
+    </row>
+    <row r="159" spans="18:18">
+      <c r="R159" s="1"/>
+    </row>
+    <row r="160" spans="18:18">
+      <c r="R160" s="1"/>
+    </row>
+    <row r="161" spans="18:18">
+      <c r="R161" s="1"/>
+    </row>
+    <row r="162" spans="18:18">
+      <c r="R162" s="1"/>
+    </row>
+    <row r="163" spans="18:18">
+      <c r="R163" s="1"/>
+    </row>
+    <row r="164" spans="18:18">
+      <c r="R164" s="1"/>
+    </row>
+    <row r="165" spans="18:18">
+      <c r="R165" s="1"/>
+    </row>
+    <row r="166" spans="18:18">
+      <c r="R166" s="1"/>
+    </row>
+    <row r="167" spans="18:18">
+      <c r="R167" s="1"/>
+    </row>
+    <row r="168" spans="18:18">
+      <c r="R168" s="1"/>
+    </row>
+    <row r="169" spans="18:18">
+      <c r="R169" s="1"/>
+    </row>
+    <row r="170" spans="18:18">
+      <c r="R170" s="1"/>
+    </row>
+    <row r="171" spans="18:18">
+      <c r="R171" s="1"/>
+    </row>
+    <row r="172" spans="18:18">
+      <c r="R172" s="1"/>
+    </row>
+    <row r="173" spans="18:18">
+      <c r="R173" s="1"/>
+    </row>
+    <row r="174" spans="18:18">
+      <c r="R174" s="1"/>
+    </row>
+    <row r="175" spans="18:18">
+      <c r="R175" s="1"/>
+    </row>
+    <row r="176" spans="18:18">
+      <c r="R176" s="1"/>
+    </row>
+    <row r="177" spans="18:18">
+      <c r="R177" s="1"/>
+    </row>
+    <row r="178" spans="18:18">
+      <c r="R178" s="1"/>
+    </row>
+    <row r="179" spans="18:18">
+      <c r="R179" s="1"/>
+    </row>
+    <row r="180" spans="18:18">
+      <c r="R180" s="1"/>
+    </row>
+    <row r="181" spans="18:18">
+      <c r="R181" s="1"/>
+    </row>
+    <row r="182" spans="18:18">
+      <c r="R182" s="1"/>
+    </row>
+    <row r="183" spans="18:18">
+      <c r="R183" s="1"/>
+    </row>
+    <row r="184" spans="18:18">
+      <c r="R184" s="1"/>
+    </row>
+    <row r="185" spans="18:18">
+      <c r="R185" s="1"/>
+    </row>
+    <row r="186" spans="18:18">
+      <c r="R186" s="1"/>
+    </row>
+    <row r="187" spans="18:18">
+      <c r="R187" s="1"/>
+    </row>
+    <row r="188" spans="18:18">
+      <c r="R188" s="1"/>
+    </row>
+    <row r="189" spans="18:18">
+      <c r="R189" s="1"/>
+    </row>
+    <row r="190" spans="18:18">
+      <c r="R190" s="1"/>
+    </row>
+    <row r="191" spans="18:18">
+      <c r="R191" s="1"/>
+    </row>
+    <row r="192" spans="18:18">
+      <c r="R192" s="1"/>
+    </row>
+    <row r="193" spans="18:18">
+      <c r="R193" s="1"/>
+    </row>
+    <row r="194" spans="18:18">
+      <c r="R194" s="1"/>
+    </row>
+    <row r="195" spans="18:18">
+      <c r="R195" s="1"/>
+    </row>
+    <row r="196" spans="18:18">
+      <c r="R196" s="1"/>
+    </row>
+    <row r="197" spans="18:18">
+      <c r="R197" s="1"/>
+    </row>
+    <row r="198" spans="18:18">
+      <c r="R198" s="1"/>
+    </row>
+    <row r="199" spans="18:18">
+      <c r="R199" s="1"/>
+    </row>
+    <row r="200" spans="18:18">
+      <c r="R200" s="1"/>
+    </row>
+    <row r="201" spans="18:18">
+      <c r="R201" s="1"/>
+    </row>
+    <row r="202" spans="18:18">
+      <c r="R202" s="1"/>
+    </row>
+    <row r="203" spans="18:18">
+      <c r="R203" s="1"/>
+    </row>
+    <row r="204" spans="18:18">
+      <c r="R204" s="1"/>
+    </row>
+    <row r="205" spans="18:18">
+      <c r="R205" s="1"/>
+    </row>
+    <row r="206" spans="18:18">
+      <c r="R206" s="1"/>
+    </row>
+    <row r="207" spans="18:18">
+      <c r="R207" s="1"/>
+    </row>
+    <row r="208" spans="18:18">
+      <c r="R208" s="1"/>
+    </row>
+    <row r="209" spans="18:18">
+      <c r="R209" s="1"/>
+    </row>
+    <row r="210" spans="18:18">
+      <c r="R210" s="1"/>
+    </row>
+    <row r="211" spans="18:18">
+      <c r="R211" s="1"/>
+    </row>
+    <row r="212" spans="18:18">
+      <c r="R212" s="1"/>
+    </row>
+    <row r="213" spans="18:18">
+      <c r="R213" s="1"/>
+    </row>
+    <row r="214" spans="18:18">
+      <c r="R214" s="1"/>
+    </row>
+    <row r="215" spans="18:18">
+      <c r="R215" s="1"/>
+    </row>
+    <row r="216" spans="18:18">
+      <c r="R216" s="1"/>
+    </row>
+    <row r="217" spans="18:18">
+      <c r="R217" s="1"/>
+    </row>
+    <row r="218" spans="18:18">
+      <c r="R218" s="1"/>
+    </row>
+    <row r="219" spans="18:18">
+      <c r="R219" s="1"/>
+    </row>
+    <row r="220" spans="18:18">
+      <c r="R220" s="1"/>
+    </row>
+    <row r="221" spans="18:18">
+      <c r="R221" s="1"/>
+    </row>
+    <row r="222" spans="18:18">
+      <c r="R222" s="1"/>
+    </row>
+    <row r="223" spans="18:18">
+      <c r="R223" s="1"/>
+    </row>
+    <row r="224" spans="18:18">
+      <c r="R224" s="1"/>
+    </row>
+    <row r="225" spans="18:18">
+      <c r="R225" s="1"/>
+    </row>
+    <row r="226" spans="18:18">
+      <c r="R226" s="1"/>
+    </row>
+    <row r="227" spans="18:18">
+      <c r="R227" s="1"/>
+    </row>
+    <row r="228" spans="18:18">
+      <c r="R228" s="1"/>
+    </row>
+    <row r="229" spans="18:18">
+      <c r="R229" s="1"/>
+    </row>
+    <row r="230" spans="18:18">
+      <c r="R230" s="1"/>
+    </row>
+    <row r="231" spans="18:18">
+      <c r="R231" s="1"/>
+    </row>
+    <row r="232" spans="18:18">
+      <c r="R232" s="1"/>
+    </row>
+    <row r="233" spans="18:18">
+      <c r="R233" s="1"/>
+    </row>
+    <row r="234" spans="18:18">
+      <c r="R234" s="1"/>
+    </row>
+    <row r="235" spans="18:18">
+      <c r="R235" s="1"/>
+    </row>
+    <row r="236" spans="18:18">
+      <c r="R236" s="1"/>
+    </row>
+    <row r="237" spans="18:18">
+      <c r="R237" s="1"/>
+    </row>
+    <row r="238" spans="18:18">
+      <c r="R238" s="1"/>
+    </row>
+    <row r="239" spans="18:18">
+      <c r="R239" s="1"/>
+    </row>
+    <row r="240" spans="18:18">
+      <c r="R240" s="1"/>
+    </row>
+    <row r="241" spans="18:18">
+      <c r="R241" s="1"/>
+    </row>
+    <row r="242" spans="18:18">
+      <c r="R242" s="1"/>
+    </row>
+    <row r="243" spans="18:18">
+      <c r="R243" s="1"/>
+    </row>
+    <row r="244" spans="18:18">
+      <c r="R244" s="1"/>
+    </row>
+    <row r="245" spans="18:18">
+      <c r="R245" s="1"/>
+    </row>
+    <row r="246" spans="18:18">
+      <c r="R246" s="1"/>
+    </row>
+    <row r="247" spans="18:18">
+      <c r="R247" s="1"/>
+    </row>
+    <row r="248" spans="18:18">
+      <c r="R248" s="1"/>
+    </row>
+    <row r="249" spans="18:18">
+      <c r="R249" s="1"/>
+    </row>
+    <row r="250" spans="18:18">
+      <c r="R250" s="1"/>
+    </row>
+    <row r="251" spans="18:18">
+      <c r="R251" s="1"/>
+    </row>
+    <row r="252" spans="18:18">
+      <c r="R252" s="1"/>
+    </row>
+    <row r="253" spans="18:18">
+      <c r="R253" s="1"/>
+    </row>
+    <row r="254" spans="18:18">
+      <c r="R254" s="1"/>
+    </row>
+    <row r="255" spans="18:18">
+      <c r="R255" s="1"/>
+    </row>
+    <row r="256" spans="18:18">
+      <c r="R256" s="1"/>
+    </row>
+    <row r="257" spans="18:18">
+      <c r="R257" s="1"/>
+    </row>
+    <row r="258" spans="18:18">
+      <c r="R258" s="1"/>
+    </row>
+    <row r="259" spans="18:18">
+      <c r="R259" s="1"/>
+    </row>
+    <row r="260" spans="18:18">
+      <c r="R260" s="1"/>
+    </row>
+    <row r="261" spans="18:18">
+      <c r="R261" s="1"/>
+    </row>
+    <row r="262" spans="18:18">
+      <c r="R262" s="1"/>
+    </row>
+    <row r="263" spans="18:18">
+      <c r="R263" s="1"/>
+    </row>
+    <row r="264" spans="18:18">
+      <c r="R264" s="1"/>
+    </row>
+    <row r="265" spans="18:18">
+      <c r="R265" s="1"/>
+    </row>
+    <row r="266" spans="18:18">
+      <c r="R266" s="1"/>
+    </row>
+    <row r="267" spans="18:18">
+      <c r="R267" s="1"/>
+    </row>
+    <row r="268" spans="18:18">
+      <c r="R268" s="1"/>
+    </row>
+    <row r="269" spans="18:18">
+      <c r="R269" s="1"/>
+    </row>
+    <row r="270" spans="18:18">
+      <c r="R270" s="1"/>
+    </row>
+    <row r="271" spans="18:18">
+      <c r="R271" s="1"/>
+    </row>
+    <row r="272" spans="18:18">
+      <c r="R272" s="1"/>
+    </row>
+    <row r="273" spans="18:18">
+      <c r="R273" s="1"/>
+    </row>
+    <row r="274" spans="18:18">
+      <c r="R274" s="1"/>
+    </row>
+    <row r="275" spans="18:18">
+      <c r="R275" s="1"/>
+    </row>
+    <row r="276" spans="18:18">
+      <c r="R276" s="1"/>
+    </row>
+    <row r="277" spans="18:18">
+      <c r="R277" s="1"/>
+    </row>
+    <row r="278" spans="18:18">
+      <c r="R278" s="1"/>
+    </row>
+    <row r="279" spans="18:18">
+      <c r="R279" s="1"/>
+    </row>
+    <row r="280" spans="18:18">
+      <c r="R280" s="1"/>
+    </row>
+    <row r="281" spans="18:18">
+      <c r="R281" s="1"/>
+    </row>
+    <row r="282" spans="18:18">
+      <c r="R282" s="1"/>
+    </row>
+    <row r="283" spans="18:18">
+      <c r="R283" s="1"/>
+    </row>
+    <row r="284" spans="18:18">
+      <c r="R284" s="1"/>
+    </row>
+    <row r="285" spans="18:18">
+      <c r="R285" s="1"/>
+    </row>
+    <row r="286" spans="18:18">
+      <c r="R286" s="1"/>
+    </row>
+    <row r="287" spans="18:18">
+      <c r="R287" s="1"/>
+    </row>
+    <row r="288" spans="18:18">
+      <c r="R288" s="1"/>
+    </row>
+    <row r="289" spans="18:18">
+      <c r="R289" s="1"/>
+    </row>
+    <row r="290" spans="18:18">
+      <c r="R290" s="1"/>
+    </row>
+    <row r="291" spans="18:18">
+      <c r="R291" s="1"/>
+    </row>
+    <row r="292" spans="18:18">
+      <c r="R292" s="1"/>
+    </row>
+    <row r="293" spans="18:18">
+      <c r="R293" s="1"/>
+    </row>
+    <row r="294" spans="18:18">
+      <c r="R294" s="1"/>
+    </row>
+    <row r="295" spans="18:18">
+      <c r="R295" s="1"/>
+    </row>
+    <row r="296" spans="18:18">
+      <c r="R296" s="1"/>
+    </row>
+    <row r="297" spans="18:18">
+      <c r="R297" s="1"/>
+    </row>
+    <row r="298" spans="18:18">
+      <c r="R298" s="1"/>
+    </row>
+    <row r="299" spans="18:18">
+      <c r="R299" s="1"/>
+    </row>
+    <row r="300" spans="18:18">
+      <c r="R300" s="1"/>
+    </row>
+    <row r="301" spans="18:18">
+      <c r="R301" s="1"/>
+    </row>
+    <row r="302" spans="18:18">
+      <c r="R302" s="1"/>
+    </row>
+    <row r="303" spans="18:18">
+      <c r="R303" s="1"/>
+    </row>
+    <row r="304" spans="18:18">
+      <c r="R304" s="1"/>
+    </row>
+    <row r="305" spans="18:18">
+      <c r="R305" s="1"/>
+    </row>
+    <row r="306" spans="18:18">
+      <c r="R306" s="1"/>
+    </row>
+    <row r="307" spans="18:18">
+      <c r="R307" s="1"/>
+    </row>
+    <row r="308" spans="18:18">
+      <c r="R308" s="1"/>
+    </row>
+    <row r="309" spans="18:18">
+      <c r="R309" s="1"/>
+    </row>
+    <row r="310" spans="18:18">
+      <c r="R310" s="1"/>
+    </row>
+    <row r="311" spans="18:18">
+      <c r="R311" s="1"/>
+    </row>
+    <row r="312" spans="18:18">
+      <c r="R312" s="1"/>
+    </row>
+    <row r="313" spans="18:18">
+      <c r="R313" s="1"/>
+    </row>
+    <row r="314" spans="18:18">
+      <c r="R314" s="1"/>
+    </row>
+    <row r="315" spans="18:18">
+      <c r="R315" s="1"/>
+    </row>
+    <row r="316" spans="18:18">
+      <c r="R316" s="1"/>
+    </row>
+    <row r="317" spans="18:18">
+      <c r="R317" s="1"/>
+    </row>
+    <row r="318" spans="18:18">
+      <c r="R318" s="1"/>
+    </row>
+    <row r="319" spans="18:18">
+      <c r="R319" s="1"/>
+    </row>
+    <row r="320" spans="18:18">
+      <c r="R320" s="1"/>
+    </row>
+    <row r="321" spans="18:18">
+      <c r="R321" s="1"/>
+    </row>
+    <row r="322" spans="18:18">
+      <c r="R322" s="1"/>
+    </row>
+    <row r="323" spans="18:18">
+      <c r="R323" s="1"/>
+    </row>
+    <row r="324" spans="18:18">
+      <c r="R324" s="1"/>
+    </row>
+    <row r="325" spans="18:18">
+      <c r="R325" s="1"/>
+    </row>
+    <row r="326" spans="18:18">
+      <c r="R326" s="1"/>
+    </row>
+    <row r="327" spans="18:18">
+      <c r="R327" s="1"/>
+    </row>
+    <row r="328" spans="18:18">
+      <c r="R328" s="1"/>
+    </row>
+    <row r="329" spans="18:18">
+      <c r="R329" s="1"/>
+    </row>
+    <row r="330" spans="18:18">
+      <c r="R330" s="1"/>
+    </row>
+    <row r="331" spans="18:18">
+      <c r="R331" s="1"/>
+    </row>
+    <row r="332" spans="18:18">
+      <c r="R332" s="1"/>
+    </row>
+    <row r="333" spans="18:18">
+      <c r="R333" s="1"/>
+    </row>
+    <row r="334" spans="18:18">
+      <c r="R334" s="1"/>
+    </row>
+    <row r="335" spans="18:18">
+      <c r="R335" s="1"/>
+    </row>
+    <row r="336" spans="18:18">
+      <c r="R336" s="1"/>
+    </row>
+    <row r="337" spans="18:18">
+      <c r="R337" s="1"/>
+    </row>
+    <row r="338" spans="18:18">
+      <c r="R338" s="1"/>
+    </row>
+    <row r="339" spans="18:18">
+      <c r="R339" s="1"/>
+    </row>
+    <row r="340" spans="18:18">
+      <c r="R340" s="1"/>
+    </row>
+    <row r="341" spans="18:18">
+      <c r="R341" s="1"/>
+    </row>
+    <row r="342" spans="18:18">
+      <c r="R342" s="1"/>
+    </row>
+    <row r="343" spans="18:18">
+      <c r="R343" s="1"/>
+    </row>
+    <row r="344" spans="18:18">
+      <c r="R344" s="1"/>
+    </row>
+    <row r="345" spans="18:18">
+      <c r="R345" s="1"/>
+    </row>
+    <row r="346" spans="18:18">
+      <c r="R346" s="1"/>
+    </row>
+    <row r="347" spans="18:18">
+      <c r="R347" s="1"/>
+    </row>
+    <row r="348" spans="18:18">
+      <c r="R348" s="1"/>
+    </row>
+    <row r="349" spans="18:18">
+      <c r="R349" s="1"/>
+    </row>
+    <row r="350" spans="18:18">
+      <c r="R350" s="1"/>
+    </row>
+    <row r="351" spans="18:18">
+      <c r="R351" s="1"/>
+    </row>
+    <row r="352" spans="18:18">
+      <c r="R352" s="1"/>
+    </row>
+    <row r="353" spans="18:18">
+      <c r="R353" s="1"/>
+    </row>
+    <row r="354" spans="18:18">
+      <c r="R354" s="1"/>
+    </row>
+    <row r="355" spans="18:18">
+      <c r="R355" s="1"/>
+    </row>
+    <row r="356" spans="18:18">
+      <c r="R356" s="1"/>
+    </row>
+    <row r="357" spans="18:18">
+      <c r="R357" s="1"/>
+    </row>
+    <row r="358" spans="18:18">
+      <c r="R358" s="1"/>
+    </row>
+    <row r="359" spans="18:18">
+      <c r="R359" s="1"/>
+    </row>
+    <row r="360" spans="18:18">
+      <c r="R360" s="1"/>
+    </row>
+    <row r="361" spans="18:18">
+      <c r="R361" s="1"/>
+    </row>
+    <row r="362" spans="18:18">
+      <c r="R362" s="1"/>
+    </row>
+    <row r="363" spans="18:18">
+      <c r="R363" s="1"/>
+    </row>
+    <row r="364" spans="18:18">
+      <c r="R364" s="1"/>
+    </row>
+    <row r="365" spans="18:18">
+      <c r="R365" s="1"/>
+    </row>
+    <row r="366" spans="18:18">
+      <c r="R366" s="1"/>
+    </row>
+    <row r="367" spans="18:18">
+      <c r="R367" s="1"/>
+    </row>
+    <row r="368" spans="18:18">
+      <c r="R368" s="1"/>
+    </row>
+    <row r="369" spans="18:18">
+      <c r="R369" s="1"/>
+    </row>
+    <row r="370" spans="18:18">
+      <c r="R370" s="1"/>
+    </row>
+    <row r="371" spans="18:18">
+      <c r="R371" s="1"/>
+    </row>
+    <row r="372" spans="18:18">
+      <c r="R372" s="1"/>
+    </row>
+    <row r="373" spans="18:18">
+      <c r="R373" s="1"/>
+    </row>
+    <row r="374" spans="18:18">
+      <c r="R374" s="1"/>
+    </row>
+    <row r="375" spans="18:18">
+      <c r="R375" s="1"/>
+    </row>
+    <row r="376" spans="18:18">
+      <c r="R376" s="1"/>
+    </row>
+    <row r="377" spans="18:18">
+      <c r="R377" s="1"/>
+    </row>
+    <row r="378" spans="18:18">
+      <c r="R378" s="1"/>
+    </row>
+    <row r="379" spans="18:18">
+      <c r="R379" s="1"/>
+    </row>
+    <row r="380" spans="18:18">
+      <c r="R380" s="1"/>
+    </row>
+    <row r="381" spans="18:18">
+      <c r="R381" s="1"/>
+    </row>
+    <row r="382" spans="18:18">
+      <c r="R382" s="1"/>
+    </row>
+    <row r="383" spans="18:18">
+      <c r="R383" s="1"/>
+    </row>
+    <row r="384" spans="18:18">
+      <c r="R384" s="1"/>
+    </row>
+    <row r="385" spans="18:18">
+      <c r="R385" s="1"/>
+    </row>
+    <row r="386" spans="18:18">
+      <c r="R386" s="1"/>
+    </row>
+    <row r="387" spans="18:18">
+      <c r="R387" s="1"/>
+    </row>
+    <row r="388" spans="18:18">
+      <c r="R388" s="1"/>
+    </row>
+    <row r="389" spans="18:18">
+      <c r="R389" s="1"/>
+    </row>
+    <row r="390" spans="18:18">
+      <c r="R390" s="1"/>
+    </row>
+    <row r="391" spans="18:18">
+      <c r="R391" s="1"/>
+    </row>
+    <row r="392" spans="18:18">
+      <c r="R392" s="1"/>
+    </row>
+    <row r="393" spans="18:18">
+      <c r="R393" s="1"/>
+    </row>
+    <row r="394" spans="18:18">
+      <c r="R394" s="1"/>
+    </row>
+    <row r="395" spans="18:18">
+      <c r="R395" s="1"/>
+    </row>
+    <row r="396" spans="18:18">
+      <c r="R396" s="1"/>
+    </row>
+    <row r="397" spans="18:18">
+      <c r="R397" s="1"/>
+    </row>
+    <row r="398" spans="18:18">
+      <c r="R398" s="1"/>
+    </row>
+    <row r="399" spans="18:18">
+      <c r="R399" s="1"/>
+    </row>
+    <row r="400" spans="18:18">
+      <c r="R400" s="1"/>
+    </row>
+    <row r="401" spans="18:18">
+      <c r="R401" s="1"/>
+    </row>
+    <row r="402" spans="18:18">
+      <c r="R402" s="1"/>
+    </row>
+    <row r="403" spans="18:18">
+      <c r="R403" s="1"/>
+    </row>
+    <row r="404" spans="18:18">
+      <c r="R404" s="1"/>
+    </row>
+    <row r="405" spans="18:18">
+      <c r="R405" s="1"/>
+    </row>
+    <row r="406" spans="18:18">
+      <c r="R406" s="1"/>
+    </row>
+    <row r="407" spans="18:18">
+      <c r="R407" s="1"/>
+    </row>
+    <row r="408" spans="18:18">
+      <c r="R408" s="1"/>
+    </row>
+    <row r="409" spans="18:18">
+      <c r="R409" s="1"/>
+    </row>
+    <row r="410" spans="18:18">
+      <c r="R410" s="1"/>
+    </row>
+    <row r="411" spans="18:18">
+      <c r="R411" s="1"/>
+    </row>
+    <row r="412" spans="18:18">
+      <c r="R412" s="1"/>
+    </row>
+    <row r="413" spans="18:18">
+      <c r="R413" s="1"/>
+    </row>
+    <row r="414" spans="18:18">
+      <c r="R414" s="1"/>
+    </row>
+    <row r="415" spans="18:18">
+      <c r="R415" s="1"/>
+    </row>
+    <row r="416" spans="18:18">
+      <c r="R416" s="1"/>
+    </row>
+    <row r="417" spans="18:18">
+      <c r="R417" s="1"/>
+    </row>
+    <row r="418" spans="18:18">
+      <c r="R418" s="1"/>
+    </row>
+    <row r="419" spans="18:18">
+      <c r="R419" s="1"/>
+    </row>
+    <row r="420" spans="18:18">
+      <c r="R420" s="1"/>
+    </row>
+    <row r="421" spans="18:18">
+      <c r="R421" s="1"/>
+    </row>
+    <row r="422" spans="18:18">
+      <c r="R422" s="1"/>
+    </row>
+    <row r="423" spans="18:18">
+      <c r="R423" s="1"/>
+    </row>
+    <row r="424" spans="18:18">
+      <c r="R424" s="1"/>
+    </row>
+    <row r="425" spans="18:18">
+      <c r="R425" s="1"/>
+    </row>
+    <row r="426" spans="18:18">
+      <c r="R426" s="1"/>
+    </row>
+    <row r="427" spans="18:18">
+      <c r="R427" s="1"/>
+    </row>
+    <row r="428" spans="18:18">
+      <c r="R428" s="1"/>
+    </row>
+    <row r="429" spans="18:18">
+      <c r="R429" s="1"/>
+    </row>
+    <row r="430" spans="18:18">
+      <c r="R430" s="1"/>
+    </row>
+    <row r="431" spans="18:18">
+      <c r="R431" s="1"/>
+    </row>
+    <row r="432" spans="18:18">
+      <c r="R432" s="1"/>
+    </row>
+    <row r="433" spans="18:18">
+      <c r="R433" s="1"/>
+    </row>
+    <row r="434" spans="18:18">
+      <c r="R434" s="1"/>
+    </row>
+    <row r="435" spans="18:18">
+      <c r="R435" s="1"/>
+    </row>
+    <row r="436" spans="18:18">
+      <c r="R436" s="1"/>
+    </row>
+    <row r="437" spans="18:18">
+      <c r="R437" s="1"/>
+    </row>
+    <row r="438" spans="18:18">
+      <c r="R438" s="1"/>
+    </row>
+    <row r="439" spans="18:18">
+      <c r="R439" s="1"/>
+    </row>
+    <row r="440" spans="18:18">
+      <c r="R440" s="1"/>
+    </row>
+    <row r="441" spans="18:18">
+      <c r="R441" s="1"/>
+    </row>
+    <row r="442" spans="18:18">
+      <c r="R442" s="1"/>
+    </row>
+    <row r="443" spans="18:18">
+      <c r="R443" s="1"/>
+    </row>
+    <row r="444" spans="18:18">
+      <c r="R444" s="1"/>
+    </row>
+    <row r="445" spans="18:18">
+      <c r="R445" s="1"/>
+    </row>
+    <row r="446" spans="18:18">
+      <c r="R446" s="1"/>
+    </row>
+    <row r="447" spans="18:18">
+      <c r="R447" s="1"/>
+    </row>
+    <row r="448" spans="18:18">
+      <c r="R448" s="1"/>
+    </row>
+    <row r="449" spans="18:18">
+      <c r="R449" s="1"/>
+    </row>
+    <row r="450" spans="18:18">
+      <c r="R450" s="1"/>
+    </row>
+    <row r="451" spans="18:18">
+      <c r="R451" s="1"/>
+    </row>
+    <row r="452" spans="18:18">
+      <c r="R452" s="1"/>
+    </row>
+    <row r="453" spans="18:18">
+      <c r="R453" s="1"/>
+    </row>
+    <row r="454" spans="18:18">
+      <c r="R454" s="1"/>
+    </row>
+    <row r="455" spans="18:18">
+      <c r="R455" s="1"/>
+    </row>
+    <row r="456" spans="18:18">
+      <c r="R456" s="1"/>
+    </row>
+    <row r="457" spans="18:18">
+      <c r="R457" s="1"/>
+    </row>
+    <row r="458" spans="18:18">
+      <c r="R458" s="1"/>
+    </row>
+    <row r="459" spans="18:18">
+      <c r="R459" s="1"/>
+    </row>
+    <row r="460" spans="18:18">
+      <c r="R460" s="1"/>
+    </row>
+    <row r="461" spans="18:18">
+      <c r="R461" s="1"/>
+    </row>
+    <row r="462" spans="18:18">
+      <c r="R462" s="1"/>
+    </row>
+    <row r="463" spans="18:18">
+      <c r="R463" s="1"/>
+    </row>
+    <row r="464" spans="18:18">
+      <c r="R464" s="1"/>
+    </row>
+    <row r="465" spans="18:18">
+      <c r="R465" s="1"/>
+    </row>
+    <row r="466" spans="18:18">
+      <c r="R466" s="1"/>
+    </row>
+    <row r="467" spans="18:18">
+      <c r="R467" s="1"/>
+    </row>
+    <row r="468" spans="18:18">
+      <c r="R468" s="1"/>
+    </row>
+    <row r="469" spans="18:18">
+      <c r="R469" s="1"/>
+    </row>
+    <row r="470" spans="18:18">
+      <c r="R470" s="1"/>
+    </row>
+    <row r="471" spans="18:18">
+      <c r="R471" s="1"/>
+    </row>
+    <row r="472" spans="18:18">
+      <c r="R472" s="1"/>
+    </row>
+    <row r="473" spans="18:18">
+      <c r="R473" s="1"/>
+    </row>
+    <row r="474" spans="18:18">
+      <c r="R474" s="1"/>
+    </row>
+    <row r="475" spans="18:18">
+      <c r="R475" s="1"/>
+    </row>
+    <row r="476" spans="18:18">
+      <c r="R476" s="1"/>
+    </row>
+    <row r="477" spans="18:18">
+      <c r="R477" s="1"/>
+    </row>
+    <row r="478" spans="18:18">
+      <c r="R478" s="1"/>
+    </row>
+    <row r="479" spans="18:18">
+      <c r="R479" s="1"/>
+    </row>
+    <row r="480" spans="18:18">
+      <c r="R480" s="1"/>
+    </row>
+    <row r="481" spans="18:18">
+      <c r="R481" s="1"/>
+    </row>
+    <row r="482" spans="18:18">
+      <c r="R482" s="1"/>
+    </row>
+    <row r="483" spans="18:18">
+      <c r="R483" s="1"/>
+    </row>
+    <row r="484" spans="18:18">
+      <c r="R484" s="1"/>
+    </row>
+    <row r="485" spans="18:18">
+      <c r="R485" s="1"/>
+    </row>
+    <row r="486" spans="18:18">
+      <c r="R486" s="1"/>
+    </row>
+    <row r="487" spans="18:18">
+      <c r="R487" s="1"/>
+    </row>
+    <row r="488" spans="18:18">
+      <c r="R488" s="1"/>
+    </row>
+    <row r="489" spans="18:18">
+      <c r="R489" s="1"/>
+    </row>
+    <row r="490" spans="18:18">
+      <c r="R490" s="1"/>
+    </row>
+    <row r="491" spans="18:18">
+      <c r="R491" s="1"/>
+    </row>
+    <row r="492" spans="18:18">
+      <c r="R492" s="1"/>
+    </row>
+    <row r="493" spans="18:18">
+      <c r="R493" s="1"/>
+    </row>
+    <row r="494" spans="18:18">
+      <c r="R494" s="1"/>
+    </row>
+    <row r="495" spans="18:18">
+      <c r="R495" s="1"/>
+    </row>
+    <row r="496" spans="18:18">
+      <c r="R496" s="1"/>
+    </row>
+    <row r="497" spans="18:18">
+      <c r="R497" s="1"/>
+    </row>
+    <row r="498" spans="18:18">
+      <c r="R498" s="1"/>
+    </row>
+    <row r="499" spans="18:18">
+      <c r="R499" s="1"/>
+    </row>
+    <row r="500" spans="18:18">
+      <c r="R500" s="1"/>
+    </row>
+    <row r="501" spans="18:18">
+      <c r="R501" s="1"/>
+    </row>
+    <row r="502" spans="18:18">
+      <c r="R502" s="1"/>
+    </row>
+    <row r="503" spans="18:18">
+      <c r="R503" s="1"/>
+    </row>
+    <row r="504" spans="18:18">
+      <c r="R504" s="1"/>
+    </row>
+    <row r="505" spans="18:18">
+      <c r="R505" s="1"/>
+    </row>
+    <row r="506" spans="18:18">
+      <c r="R506" s="1"/>
+    </row>
+    <row r="507" spans="18:18">
+      <c r="R507" s="1"/>
+    </row>
+    <row r="508" spans="18:18">
+      <c r="R508" s="1"/>
+    </row>
+    <row r="509" spans="18:18">
+      <c r="R509" s="1"/>
+    </row>
+    <row r="510" spans="18:18">
+      <c r="R510" s="1"/>
+    </row>
+    <row r="511" spans="18:18">
+      <c r="R511" s="1"/>
+    </row>
+    <row r="512" spans="18:18">
+      <c r="R512" s="1"/>
+    </row>
+    <row r="513" spans="18:18">
+      <c r="R513" s="1"/>
+    </row>
+    <row r="514" spans="18:18">
+      <c r="R514" s="1"/>
+    </row>
+    <row r="515" spans="18:18">
+      <c r="R515" s="1"/>
+    </row>
+    <row r="516" spans="18:18">
+      <c r="R516" s="1"/>
+    </row>
+    <row r="517" spans="18:18">
+      <c r="R517" s="1"/>
+    </row>
+    <row r="518" spans="18:18">
+      <c r="R518" s="1"/>
+    </row>
+    <row r="519" spans="18:18">
+      <c r="R519" s="1"/>
+    </row>
+    <row r="520" spans="18:18">
+      <c r="R520" s="1"/>
+    </row>
+    <row r="521" spans="18:18">
+      <c r="R521" s="1"/>
+    </row>
+    <row r="522" spans="18:18">
+      <c r="R522" s="1"/>
+    </row>
+    <row r="523" spans="18:18">
+      <c r="R523" s="1"/>
+    </row>
+    <row r="524" spans="18:18">
+      <c r="R524" s="1"/>
+    </row>
+    <row r="525" spans="18:18">
+      <c r="R525" s="1"/>
+    </row>
+    <row r="526" spans="18:18">
+      <c r="R526" s="1"/>
+    </row>
+    <row r="527" spans="18:18">
+      <c r="R527" s="1"/>
+    </row>
+    <row r="528" spans="18:18">
+      <c r="R528" s="1"/>
+    </row>
+    <row r="529" spans="18:18">
+      <c r="R529" s="1"/>
+    </row>
+    <row r="530" spans="18:18">
+      <c r="R530" s="1"/>
+    </row>
+    <row r="531" spans="18:18">
+      <c r="R531" s="1"/>
+    </row>
+    <row r="532" spans="18:18">
+      <c r="R532" s="1"/>
+    </row>
+    <row r="533" spans="18:18">
+      <c r="R533" s="1"/>
+    </row>
+    <row r="534" spans="18:18">
+      <c r="R534" s="1"/>
+    </row>
+    <row r="535" spans="18:18">
+      <c r="R535" s="1"/>
+    </row>
+    <row r="536" spans="18:18">
+      <c r="R536" s="1"/>
+    </row>
+    <row r="537" spans="18:18">
+      <c r="R537" s="1"/>
+    </row>
+    <row r="538" spans="18:18">
+      <c r="R538" s="1"/>
+    </row>
+    <row r="539" spans="18:18">
+      <c r="R539" s="1"/>
+    </row>
+    <row r="540" spans="18:18">
+      <c r="R540" s="1"/>
+    </row>
+    <row r="541" spans="18:18">
+      <c r="R541" s="1"/>
+    </row>
+    <row r="542" spans="18:18">
+      <c r="R542" s="1"/>
+    </row>
+    <row r="543" spans="18:18">
+      <c r="R543" s="1"/>
+    </row>
+    <row r="544" spans="18:18">
+      <c r="R544" s="1"/>
+    </row>
+    <row r="545" spans="18:18">
+      <c r="R545" s="1"/>
+    </row>
+    <row r="546" spans="18:18">
+      <c r="R546" s="1"/>
+    </row>
+    <row r="547" spans="18:18">
+      <c r="R547" s="1"/>
+    </row>
+    <row r="548" spans="18:18">
+      <c r="R548" s="1"/>
+    </row>
+    <row r="549" spans="18:18">
+      <c r="R549" s="1"/>
+    </row>
+    <row r="550" spans="18:18">
+      <c r="R550" s="1"/>
+    </row>
+    <row r="551" spans="18:18">
+      <c r="R551" s="1"/>
+    </row>
+    <row r="552" spans="18:18">
+      <c r="R552" s="1"/>
+    </row>
+    <row r="553" spans="18:18">
+      <c r="R553" s="1"/>
+    </row>
+    <row r="554" spans="18:18">
+      <c r="R554" s="1"/>
+    </row>
+    <row r="555" spans="18:18">
+      <c r="R555" s="1"/>
+    </row>
+    <row r="556" spans="18:18">
+      <c r="R556" s="1"/>
+    </row>
+    <row r="557" spans="18:18">
+      <c r="R557" s="1"/>
+    </row>
+    <row r="558" spans="18:18">
+      <c r="R558" s="1"/>
+    </row>
+    <row r="559" spans="18:18">
+      <c r="R559" s="1"/>
+    </row>
+    <row r="560" spans="18:18">
+      <c r="R560" s="1"/>
+    </row>
+    <row r="561" spans="18:18">
+      <c r="R561" s="1"/>
+    </row>
+    <row r="562" spans="18:18">
+      <c r="R562" s="1"/>
+    </row>
+    <row r="563" spans="18:18">
+      <c r="R563" s="1"/>
+    </row>
+    <row r="564" spans="18:18">
+      <c r="R564" s="1"/>
+    </row>
+    <row r="565" spans="18:18">
+      <c r="R565" s="1"/>
+    </row>
+    <row r="566" spans="18:18">
+      <c r="R566" s="1"/>
+    </row>
+    <row r="567" spans="18:18">
+      <c r="R567" s="1"/>
+    </row>
+    <row r="568" spans="18:18">
+      <c r="R568" s="1"/>
+    </row>
+    <row r="569" spans="18:18">
+      <c r="R569" s="1"/>
+    </row>
+    <row r="570" spans="18:18">
+      <c r="R570" s="1"/>
+    </row>
+    <row r="571" spans="18:18">
+      <c r="R571" s="1"/>
+    </row>
+    <row r="572" spans="18:18">
+      <c r="R572" s="1"/>
+    </row>
+    <row r="573" spans="18:18">
+      <c r="R573" s="1"/>
+    </row>
+    <row r="574" spans="18:18">
+      <c r="R574" s="1"/>
+    </row>
+    <row r="575" spans="18:18">
+      <c r="R575" s="1"/>
+    </row>
+    <row r="576" spans="18:18">
+      <c r="R576" s="1"/>
+    </row>
+    <row r="577" spans="18:18">
+      <c r="R577" s="1"/>
+    </row>
+    <row r="578" spans="18:18">
+      <c r="R578" s="1"/>
+    </row>
+    <row r="579" spans="18:18">
+      <c r="R579" s="1"/>
+    </row>
+    <row r="580" spans="18:18">
+      <c r="R580" s="1"/>
+    </row>
+    <row r="581" spans="18:18">
+      <c r="R581" s="1"/>
+    </row>
+    <row r="582" spans="18:18">
+      <c r="R582" s="1"/>
+    </row>
+    <row r="583" spans="18:18">
+      <c r="R583" s="1"/>
+    </row>
+    <row r="584" spans="18:18">
+      <c r="R584" s="1"/>
+    </row>
+    <row r="585" spans="18:18">
+      <c r="R585" s="1"/>
+    </row>
+    <row r="586" spans="18:18">
+      <c r="R586" s="1"/>
+    </row>
+    <row r="587" spans="18:18">
+      <c r="R587" s="1"/>
+    </row>
+    <row r="588" spans="18:18">
+      <c r="R588" s="1"/>
+    </row>
+    <row r="589" spans="18:18">
+      <c r="R589" s="1"/>
+    </row>
+    <row r="590" spans="18:18">
+      <c r="R590" s="1"/>
+    </row>
+    <row r="591" spans="18:18">
+      <c r="R591" s="1"/>
+    </row>
+    <row r="592" spans="18:18">
+      <c r="R592" s="1"/>
+    </row>
+    <row r="593" spans="18:18">
+      <c r="R593" s="1"/>
+    </row>
+    <row r="594" spans="18:18">
+      <c r="R594" s="1"/>
+    </row>
+    <row r="595" spans="18:18">
+      <c r="R595" s="1"/>
+    </row>
+    <row r="596" spans="18:18">
+      <c r="R596" s="1"/>
+    </row>
+    <row r="597" spans="18:18">
+      <c r="R597" s="1"/>
+    </row>
+    <row r="598" spans="18:18">
+      <c r="R598" s="1"/>
+    </row>
+    <row r="599" spans="18:18">
+      <c r="R599" s="1"/>
+    </row>
+    <row r="600" spans="18:18">
+      <c r="R600" s="1"/>
+    </row>
+    <row r="601" spans="18:18">
+      <c r="R601" s="1"/>
+    </row>
+    <row r="602" spans="18:18">
+      <c r="R602" s="1"/>
+    </row>
+    <row r="603" spans="18:18">
+      <c r="R603" s="1"/>
+    </row>
+    <row r="604" spans="18:18">
+      <c r="R604" s="1"/>
+    </row>
+    <row r="605" spans="18:18">
+      <c r="R605" s="1"/>
+    </row>
+    <row r="606" spans="18:18">
+      <c r="R606" s="1"/>
+    </row>
+    <row r="607" spans="18:18">
+      <c r="R607" s="1"/>
+    </row>
+    <row r="608" spans="18:18">
+      <c r="R608" s="1"/>
+    </row>
+    <row r="609" spans="18:18">
+      <c r="R609" s="1"/>
+    </row>
+    <row r="610" spans="18:18">
+      <c r="R610" s="1"/>
+    </row>
+    <row r="611" spans="18:18">
+      <c r="R611" s="1"/>
+    </row>
+    <row r="612" spans="18:18">
+      <c r="R612" s="1"/>
+    </row>
+    <row r="613" spans="18:18">
+      <c r="R613" s="1"/>
+    </row>
+    <row r="614" spans="18:18">
+      <c r="R614" s="1"/>
+    </row>
+    <row r="615" spans="18:18">
+      <c r="R615" s="1"/>
+    </row>
+    <row r="616" spans="18:18">
+      <c r="R616" s="1"/>
+    </row>
+    <row r="617" spans="18:18">
+      <c r="R617" s="1"/>
+    </row>
+    <row r="618" spans="18:18">
+      <c r="R618" s="1"/>
+    </row>
+    <row r="619" spans="18:18">
+      <c r="R619" s="1"/>
+    </row>
+    <row r="620" spans="18:18">
+      <c r="R620" s="1"/>
+    </row>
+    <row r="621" spans="18:18">
+      <c r="R621" s="1"/>
+    </row>
+    <row r="622" spans="18:18">
+      <c r="R622" s="1"/>
+    </row>
+    <row r="623" spans="18:18">
+      <c r="R623" s="1"/>
+    </row>
+    <row r="624" spans="18:18">
+      <c r="R624" s="1"/>
+    </row>
+    <row r="625" spans="18:18">
+      <c r="R625" s="1"/>
+    </row>
+    <row r="626" spans="18:18">
+      <c r="R626" s="1"/>
+    </row>
+    <row r="627" spans="18:18">
+      <c r="R627" s="1"/>
+    </row>
+    <row r="628" spans="18:18">
+      <c r="R628" s="1"/>
+    </row>
+    <row r="629" spans="18:18">
+      <c r="R629" s="1"/>
+    </row>
+    <row r="630" spans="18:18">
+      <c r="R630" s="1"/>
+    </row>
+    <row r="631" spans="18:18">
+      <c r="R631" s="1"/>
+    </row>
+    <row r="632" spans="18:18">
+      <c r="R632" s="1"/>
+    </row>
+    <row r="633" spans="18:18">
+      <c r="R633" s="1"/>
+    </row>
+    <row r="634" spans="18:18">
+      <c r="R634" s="1"/>
+    </row>
+    <row r="635" spans="18:18">
+      <c r="R635" s="1"/>
+    </row>
+    <row r="636" spans="18:18">
+      <c r="R636" s="1"/>
+    </row>
+    <row r="637" spans="18:18">
+      <c r="R637" s="1"/>
+    </row>
+    <row r="638" spans="18:18">
+      <c r="R638" s="1"/>
+    </row>
+    <row r="639" spans="18:18">
+      <c r="R639" s="1"/>
+    </row>
+    <row r="640" spans="18:18">
+      <c r="R640" s="1"/>
+    </row>
+    <row r="641" spans="18:18">
+      <c r="R641" s="1"/>
+    </row>
+    <row r="642" spans="18:18">
+      <c r="R642" s="1"/>
+    </row>
+    <row r="643" spans="18:18">
+      <c r="R643" s="1"/>
+    </row>
+    <row r="644" spans="18:18">
+      <c r="R644" s="1"/>
+    </row>
+    <row r="645" spans="18:18">
+      <c r="R645" s="1"/>
+    </row>
+    <row r="646" spans="18:18">
+      <c r="R646" s="1"/>
+    </row>
+    <row r="647" spans="18:18">
+      <c r="R647" s="1"/>
+    </row>
+    <row r="648" spans="18:18">
+      <c r="R648" s="1"/>
+    </row>
+    <row r="649" spans="18:18">
+      <c r="R649" s="1"/>
+    </row>
+    <row r="650" spans="18:18">
+      <c r="R650" s="1"/>
+    </row>
+    <row r="651" spans="18:18">
+      <c r="R651" s="1"/>
+    </row>
+    <row r="652" spans="18:18">
+      <c r="R652" s="1"/>
+    </row>
+    <row r="653" spans="18:18">
+      <c r="R653" s="1"/>
+    </row>
+    <row r="654" spans="18:18">
+      <c r="R654" s="1"/>
+    </row>
+    <row r="655" spans="18:18">
+      <c r="R655" s="1"/>
+    </row>
+    <row r="656" spans="18:18">
+      <c r="R656" s="1"/>
+    </row>
+    <row r="657" spans="18:18">
+      <c r="R657" s="1"/>
+    </row>
+    <row r="658" spans="18:18">
+      <c r="R658" s="1"/>
+    </row>
+    <row r="659" spans="18:18">
+      <c r="R659" s="1"/>
+    </row>
+    <row r="660" spans="18:18">
+      <c r="R660" s="1"/>
+    </row>
+    <row r="661" spans="18:18">
+      <c r="R661" s="1"/>
+    </row>
+    <row r="662" spans="18:18">
+      <c r="R662" s="1"/>
+    </row>
+    <row r="663" spans="18:18">
+      <c r="R663" s="1"/>
+    </row>
+    <row r="664" spans="18:18">
+      <c r="R664" s="1"/>
+    </row>
+    <row r="665" spans="18:18">
+      <c r="R665" s="1"/>
+    </row>
+    <row r="666" spans="18:18">
+      <c r="R666" s="1"/>
+    </row>
+    <row r="667" spans="18:18">
+      <c r="R667" s="1"/>
+    </row>
+    <row r="668" spans="18:18">
+      <c r="R668" s="1"/>
+    </row>
+    <row r="669" spans="18:18">
+      <c r="R669" s="1"/>
+    </row>
+    <row r="670" spans="18:18">
+      <c r="R670" s="1"/>
+    </row>
+    <row r="671" spans="18:18">
+      <c r="R671" s="1"/>
+    </row>
+    <row r="672" spans="18:18">
+      <c r="R672" s="1"/>
+    </row>
+    <row r="673" spans="18:18">
+      <c r="R673" s="1"/>
+    </row>
+    <row r="674" spans="18:18">
+      <c r="R674" s="1"/>
+    </row>
+    <row r="675" spans="18:18">
+      <c r="R675" s="1"/>
+    </row>
+    <row r="676" spans="18:18">
+      <c r="R676" s="1"/>
+    </row>
+    <row r="677" spans="18:18">
+      <c r="R677" s="1"/>
+    </row>
+    <row r="678" spans="18:18">
+      <c r="R678" s="1"/>
+    </row>
+    <row r="679" spans="18:18">
+      <c r="R679" s="1"/>
+    </row>
+    <row r="680" spans="18:18">
+      <c r="R680" s="1"/>
+    </row>
+    <row r="681" spans="18:18">
+      <c r="R681" s="1"/>
+    </row>
+    <row r="682" spans="18:18">
+      <c r="R682" s="1"/>
+    </row>
+    <row r="683" spans="18:18">
+      <c r="R683" s="1"/>
+    </row>
+    <row r="684" spans="18:18">
+      <c r="R684" s="1"/>
+    </row>
+    <row r="685" spans="18:18">
+      <c r="R685" s="1"/>
+    </row>
+    <row r="686" spans="18:18">
+      <c r="R686" s="1"/>
+    </row>
+    <row r="687" spans="18:18">
+      <c r="R687" s="1"/>
+    </row>
+    <row r="688" spans="18:18">
+      <c r="R688" s="1"/>
+    </row>
+    <row r="689" spans="18:18">
+      <c r="R689" s="1"/>
+    </row>
+    <row r="690" spans="18:18">
+      <c r="R690" s="1"/>
+    </row>
+    <row r="691" spans="18:18">
+      <c r="R691" s="1"/>
+    </row>
+    <row r="692" spans="18:18">
+      <c r="R692" s="1"/>
+    </row>
+    <row r="693" spans="18:18">
+      <c r="R693" s="1"/>
+    </row>
+    <row r="694" spans="18:18">
+      <c r="R694" s="1"/>
+    </row>
+    <row r="695" spans="18:18">
+      <c r="R695" s="1"/>
+    </row>
+    <row r="696" spans="18:18">
+      <c r="R696" s="1"/>
+    </row>
+    <row r="697" spans="18:18">
+      <c r="R697" s="1"/>
+    </row>
+    <row r="698" spans="18:18">
+      <c r="R698" s="1"/>
+    </row>
+    <row r="699" spans="18:18">
+      <c r="R699" s="1"/>
+    </row>
+    <row r="700" spans="18:18">
+      <c r="R700" s="1"/>
+    </row>
+    <row r="701" spans="18:18">
+      <c r="R701" s="1"/>
+    </row>
+    <row r="702" spans="18:18">
+      <c r="R702" s="1"/>
+    </row>
+    <row r="703" spans="18:18">
+      <c r="R703" s="1"/>
+    </row>
+    <row r="704" spans="18:18">
+      <c r="R704" s="1"/>
+    </row>
+    <row r="705" spans="18:18">
+      <c r="R705" s="1"/>
+    </row>
+    <row r="706" spans="18:18">
+      <c r="R706" s="1"/>
+    </row>
+    <row r="707" spans="18:18">
+      <c r="R707" s="1"/>
+    </row>
+    <row r="708" spans="18:18">
+      <c r="R708" s="1"/>
+    </row>
+    <row r="709" spans="18:18">
+      <c r="R709" s="1"/>
+    </row>
+    <row r="710" spans="18:18">
+      <c r="R710" s="1"/>
+    </row>
+    <row r="711" spans="18:18">
+      <c r="R711" s="1"/>
+    </row>
+    <row r="712" spans="18:18">
+      <c r="R712" s="1"/>
+    </row>
+    <row r="713" spans="18:18">
+      <c r="R713" s="1"/>
+    </row>
+    <row r="714" spans="18:18">
+      <c r="R714" s="1"/>
+    </row>
+    <row r="715" spans="18:18">
+      <c r="R715" s="1"/>
+    </row>
+    <row r="716" spans="18:18">
+      <c r="R716" s="1"/>
+    </row>
+    <row r="717" spans="18:18">
+      <c r="R717" s="1"/>
+    </row>
+    <row r="718" spans="18:18">
+      <c r="R718" s="1"/>
+    </row>
+    <row r="719" spans="18:18">
+      <c r="R719" s="1"/>
+    </row>
+    <row r="720" spans="18:18">
+      <c r="R720" s="1"/>
+    </row>
+    <row r="721" spans="18:18">
+      <c r="R721" s="1"/>
+    </row>
+    <row r="722" spans="18:18">
+      <c r="R722" s="1"/>
+    </row>
+    <row r="723" spans="18:18">
+      <c r="R723" s="1"/>
+    </row>
+    <row r="724" spans="18:18">
+      <c r="R724" s="1"/>
+    </row>
+    <row r="725" spans="18:18">
+      <c r="R725" s="1"/>
+    </row>
+    <row r="726" spans="18:18">
+      <c r="R726" s="1"/>
+    </row>
+    <row r="727" spans="18:18">
+      <c r="R727" s="1"/>
+    </row>
+    <row r="728" spans="18:18">
+      <c r="R728" s="1"/>
+    </row>
+    <row r="729" spans="18:18">
+      <c r="R729" s="1"/>
+    </row>
+    <row r="730" spans="18:18">
+      <c r="R730" s="1"/>
+    </row>
+    <row r="731" spans="18:18">
+      <c r="R731" s="1"/>
+    </row>
+    <row r="732" spans="18:18">
+      <c r="R732" s="1"/>
+    </row>
+    <row r="733" spans="18:18">
+      <c r="R733" s="1"/>
+    </row>
+    <row r="734" spans="18:18">
+      <c r="R734" s="1"/>
+    </row>
+    <row r="735" spans="18:18">
+      <c r="R735" s="1"/>
+    </row>
+    <row r="736" spans="18:18">
+      <c r="R736" s="1"/>
+    </row>
+    <row r="737" spans="18:18">
+      <c r="R737" s="1"/>
+    </row>
+    <row r="738" spans="18:18">
+      <c r="R738" s="1"/>
+    </row>
+    <row r="739" spans="18:18">
+      <c r="R739" s="1"/>
+    </row>
+    <row r="740" spans="18:18">
+      <c r="R740" s="1"/>
+    </row>
+    <row r="741" spans="18:18">
+      <c r="R741" s="1"/>
+    </row>
+    <row r="742" spans="18:18">
+      <c r="R742" s="1"/>
+    </row>
+    <row r="743" spans="18:18">
+      <c r="R743" s="1"/>
+    </row>
+    <row r="744" spans="18:18">
+      <c r="R744" s="1"/>
+    </row>
+    <row r="745" spans="18:18">
+      <c r="R745" s="1"/>
+    </row>
+    <row r="746" spans="18:18">
+      <c r="R746" s="1"/>
+    </row>
+    <row r="747" spans="18:18">
+      <c r="R747" s="1"/>
+    </row>
+    <row r="748" spans="18:18">
+      <c r="R748" s="1"/>
+    </row>
+    <row r="749" spans="18:18">
+      <c r="R749" s="1"/>
+    </row>
+    <row r="750" spans="18:18">
+      <c r="R750" s="1"/>
+    </row>
+    <row r="751" spans="18:18">
+      <c r="R751" s="1"/>
+    </row>
+    <row r="752" spans="18:18">
+      <c r="R752" s="1"/>
+    </row>
+    <row r="753" spans="18:18">
+      <c r="R753" s="1"/>
+    </row>
+    <row r="754" spans="18:18">
+      <c r="R754" s="1"/>
+    </row>
+    <row r="755" spans="18:18">
+      <c r="R755" s="1"/>
+    </row>
+    <row r="756" spans="18:18">
+      <c r="R756" s="1"/>
+    </row>
+    <row r="757" spans="18:18">
+      <c r="R757" s="1"/>
+    </row>
+    <row r="758" spans="18:18">
+      <c r="R758" s="1"/>
+    </row>
+    <row r="759" spans="18:18">
+      <c r="R759" s="1"/>
+    </row>
+    <row r="760" spans="18:18">
+      <c r="R760" s="1"/>
+    </row>
+    <row r="761" spans="18:18">
+      <c r="R761" s="1"/>
+    </row>
+    <row r="762" spans="18:18">
+      <c r="R762" s="1"/>
+    </row>
+    <row r="763" spans="18:18">
+      <c r="R763" s="1"/>
+    </row>
+    <row r="764" spans="18:18">
+      <c r="R764" s="1"/>
+    </row>
+    <row r="765" spans="18:18">
+      <c r="R765" s="1"/>
+    </row>
+    <row r="766" spans="18:18">
+      <c r="R766" s="1"/>
+    </row>
+    <row r="767" spans="18:18">
+      <c r="R767" s="1"/>
+    </row>
+    <row r="768" spans="18:18">
+      <c r="R768" s="1"/>
+    </row>
+    <row r="769" spans="18:18">
+      <c r="R769" s="1"/>
+    </row>
+    <row r="770" spans="18:18">
+      <c r="R770" s="1"/>
+    </row>
+    <row r="771" spans="18:18">
+      <c r="R771" s="1"/>
+    </row>
+    <row r="772" spans="18:18">
+      <c r="R772" s="1"/>
+    </row>
+    <row r="773" spans="18:18">
+      <c r="R773" s="1"/>
+    </row>
+    <row r="774" spans="18:18">
+      <c r="R774" s="1"/>
+    </row>
+    <row r="775" spans="18:18">
+      <c r="R775" s="1"/>
+    </row>
+    <row r="776" spans="18:18">
+      <c r="R776" s="1"/>
+    </row>
+    <row r="777" spans="18:18">
+      <c r="R777" s="1"/>
+    </row>
+    <row r="778" spans="18:18">
+      <c r="R778" s="1"/>
+    </row>
+    <row r="779" spans="18:18">
+      <c r="R779" s="1"/>
+    </row>
+    <row r="780" spans="18:18">
+      <c r="R780" s="1"/>
+    </row>
+    <row r="781" spans="18:18">
+      <c r="R781" s="1"/>
+    </row>
+    <row r="782" spans="18:18">
+      <c r="R782" s="1"/>
+    </row>
+    <row r="783" spans="18:18">
+      <c r="R783" s="1"/>
+    </row>
+    <row r="784" spans="18:18">
+      <c r="R784" s="1"/>
+    </row>
+    <row r="785" spans="18:18">
+      <c r="R785" s="1"/>
+    </row>
+    <row r="786" spans="18:18">
+      <c r="R786" s="1"/>
+    </row>
+    <row r="787" spans="18:18">
+      <c r="R787" s="1"/>
+    </row>
+    <row r="788" spans="18:18">
+      <c r="R788" s="1"/>
+    </row>
+    <row r="789" spans="18:18">
+      <c r="R789" s="1"/>
+    </row>
+    <row r="790" spans="18:18">
+      <c r="R790" s="1"/>
+    </row>
+    <row r="791" spans="18:18">
+      <c r="R791" s="1"/>
+    </row>
+    <row r="792" spans="18:18">
+      <c r="R792" s="1"/>
+    </row>
+    <row r="793" spans="18:18">
+      <c r="R793" s="1"/>
+    </row>
+    <row r="794" spans="18:18">
+      <c r="R794" s="1"/>
+    </row>
+    <row r="795" spans="18:18">
+      <c r="R795" s="1"/>
+    </row>
+    <row r="796" spans="18:18">
+      <c r="R796" s="1"/>
+    </row>
+    <row r="797" spans="18:18">
+      <c r="R797" s="1"/>
+    </row>
+    <row r="798" spans="18:18">
+      <c r="R798" s="1"/>
+    </row>
+    <row r="799" spans="18:18">
+      <c r="R799" s="1"/>
+    </row>
+    <row r="800" spans="18:18">
+      <c r="R800" s="1"/>
+    </row>
+    <row r="801" spans="18:18">
+      <c r="R801" s="1"/>
+    </row>
+    <row r="802" spans="18:18">
+      <c r="R802" s="1"/>
+    </row>
+    <row r="803" spans="18:18">
+      <c r="R803" s="1"/>
+    </row>
+    <row r="804" spans="18:18">
+      <c r="R804" s="1"/>
+    </row>
+    <row r="805" spans="18:18">
+      <c r="R805" s="1"/>
+    </row>
+    <row r="806" spans="18:18">
+      <c r="R806" s="1"/>
+    </row>
+    <row r="807" spans="18:18">
+      <c r="R807" s="1"/>
+    </row>
+    <row r="808" spans="18:18">
+      <c r="R808" s="1"/>
+    </row>
+    <row r="809" spans="18:18">
+      <c r="R809" s="1"/>
+    </row>
+    <row r="810" spans="18:18">
+      <c r="R810" s="1"/>
+    </row>
+    <row r="811" spans="18:18">
+      <c r="R811" s="1"/>
+    </row>
+    <row r="812" spans="18:18">
+      <c r="R812" s="1"/>
+    </row>
+    <row r="813" spans="18:18">
+      <c r="R813" s="1"/>
+    </row>
+    <row r="814" spans="18:18">
+      <c r="R814" s="1"/>
+    </row>
+    <row r="815" spans="18:18">
+      <c r="R815" s="1"/>
+    </row>
+    <row r="816" spans="18:18">
+      <c r="R816" s="1"/>
+    </row>
+    <row r="817" spans="18:18">
+      <c r="R817" s="1"/>
+    </row>
+    <row r="818" spans="18:18">
+      <c r="R818" s="1"/>
+    </row>
+    <row r="819" spans="18:18">
+      <c r="R819" s="1"/>
+    </row>
+    <row r="820" spans="18:18">
+      <c r="R820" s="1"/>
+    </row>
+    <row r="821" spans="18:18">
+      <c r="R821" s="1"/>
+    </row>
+    <row r="822" spans="18:18">
+      <c r="R822" s="1"/>
+    </row>
+    <row r="823" spans="18:18">
+      <c r="R823" s="1"/>
+    </row>
+    <row r="824" spans="18:18">
+      <c r="R824" s="1"/>
+    </row>
+    <row r="825" spans="18:18">
+      <c r="R825" s="1"/>
+    </row>
+    <row r="826" spans="18:18">
+      <c r="R826" s="1"/>
+    </row>
+    <row r="827" spans="18:18">
+      <c r="R827" s="1"/>
+    </row>
+    <row r="828" spans="18:18">
+      <c r="R828" s="1"/>
+    </row>
+    <row r="829" spans="18:18">
+      <c r="R829" s="1"/>
+    </row>
+    <row r="830" spans="18:18">
+      <c r="R830" s="1"/>
+    </row>
+    <row r="831" spans="18:18">
+      <c r="R831" s="1"/>
+    </row>
+    <row r="832" spans="18:18">
+      <c r="R832" s="1"/>
+    </row>
+    <row r="833" spans="18:18">
+      <c r="R833" s="1"/>
+    </row>
+    <row r="834" spans="18:18">
+      <c r="R834" s="1"/>
+    </row>
+    <row r="835" spans="18:18">
+      <c r="R835" s="1"/>
+    </row>
+    <row r="836" spans="18:18">
+      <c r="R836" s="1"/>
+    </row>
+    <row r="837" spans="18:18">
+      <c r="R837" s="1"/>
+    </row>
+    <row r="838" spans="18:18">
+      <c r="R838" s="1"/>
+    </row>
+    <row r="839" spans="18:18">
+      <c r="R839" s="1"/>
+    </row>
+    <row r="840" spans="18:18">
+      <c r="R840" s="1"/>
+    </row>
+    <row r="841" spans="18:18">
+      <c r="R841" s="1"/>
+    </row>
+    <row r="842" spans="18:18">
+      <c r="R842" s="1"/>
+    </row>
+    <row r="843" spans="18:18">
+      <c r="R843" s="1"/>
+    </row>
+    <row r="844" spans="18:18">
+      <c r="R844" s="1"/>
+    </row>
+    <row r="845" spans="18:18">
+      <c r="R845" s="1"/>
+    </row>
+    <row r="846" spans="18:18">
+      <c r="R846" s="1"/>
+    </row>
+    <row r="847" spans="18:18">
+      <c r="R847" s="1"/>
+    </row>
+    <row r="848" spans="18:18">
+      <c r="R848" s="1"/>
+    </row>
+    <row r="849" spans="18:18">
+      <c r="R849" s="1"/>
+    </row>
+    <row r="850" spans="18:18">
+      <c r="R850" s="1"/>
+    </row>
+    <row r="851" spans="18:18">
+      <c r="R851" s="1"/>
+    </row>
+    <row r="852" spans="18:18">
+      <c r="R852" s="1"/>
+    </row>
+    <row r="853" spans="18:18">
+      <c r="R853" s="1"/>
+    </row>
+    <row r="854" spans="18:18">
+      <c r="R854" s="1"/>
+    </row>
+    <row r="855" spans="18:18">
+      <c r="R855" s="1"/>
+    </row>
+    <row r="856" spans="18:18">
+      <c r="R856" s="1"/>
+    </row>
+    <row r="857" spans="18:18">
+      <c r="R857" s="1"/>
+    </row>
+    <row r="858" spans="18:18">
+      <c r="R858" s="1"/>
+    </row>
+    <row r="859" spans="18:18">
+      <c r="R859" s="1"/>
+    </row>
+    <row r="860" spans="18:18">
+      <c r="R860" s="1"/>
+    </row>
+    <row r="861" spans="18:18">
+      <c r="R861" s="1"/>
+    </row>
+    <row r="862" spans="18:18">
+      <c r="R862" s="1"/>
+    </row>
+    <row r="863" spans="18:18">
+      <c r="R863" s="1"/>
+    </row>
+    <row r="864" spans="18:18">
+      <c r="R864" s="1"/>
+    </row>
+    <row r="865" spans="18:18">
+      <c r="R865" s="1"/>
+    </row>
+    <row r="866" spans="18:18">
+      <c r="R866" s="1"/>
+    </row>
+    <row r="867" spans="18:18">
+      <c r="R867" s="1"/>
+    </row>
+    <row r="868" spans="18:18">
+      <c r="R868" s="1"/>
+    </row>
+    <row r="869" spans="18:18">
+      <c r="R869" s="1"/>
+    </row>
+    <row r="870" spans="18:18">
+      <c r="R870" s="1"/>
+    </row>
+    <row r="871" spans="18:18">
+      <c r="R871" s="1"/>
+    </row>
+    <row r="872" spans="18:18">
+      <c r="R872" s="1"/>
+    </row>
+    <row r="873" spans="18:18">
+      <c r="R873" s="1"/>
+    </row>
+    <row r="874" spans="18:18">
+      <c r="R874" s="1"/>
+    </row>
+    <row r="875" spans="18:18">
+      <c r="R875" s="1"/>
+    </row>
+    <row r="876" spans="18:18">
+      <c r="R876" s="1"/>
+    </row>
+    <row r="877" spans="18:18">
+      <c r="R877" s="1"/>
+    </row>
+    <row r="878" spans="18:18">
+      <c r="R878" s="1"/>
+    </row>
+    <row r="879" spans="18:18">
+      <c r="R879" s="1"/>
+    </row>
+    <row r="880" spans="18:18">
+      <c r="R880" s="1"/>
+    </row>
+    <row r="881" spans="18:18">
+      <c r="R881" s="1"/>
+    </row>
+    <row r="882" spans="18:18">
+      <c r="R882" s="1"/>
+    </row>
+    <row r="883" spans="18:18">
+      <c r="R883" s="1"/>
+    </row>
+    <row r="884" spans="18:18">
+      <c r="R884" s="1"/>
+    </row>
+    <row r="885" spans="18:18">
+      <c r="R885" s="1"/>
+    </row>
+    <row r="886" spans="18:18">
+      <c r="R886" s="1"/>
+    </row>
+    <row r="887" spans="18:18">
+      <c r="R887" s="1"/>
+    </row>
+    <row r="888" spans="18:18">
+      <c r="R888" s="1"/>
+    </row>
+    <row r="889" spans="18:18">
+      <c r="R889" s="1"/>
+    </row>
+    <row r="890" spans="18:18">
+      <c r="R890" s="1"/>
+    </row>
+    <row r="891" spans="18:18">
+      <c r="R891" s="1"/>
+    </row>
+    <row r="892" spans="18:18">
+      <c r="R892" s="1"/>
+    </row>
+    <row r="893" spans="18:18">
+      <c r="R893" s="1"/>
+    </row>
+    <row r="894" spans="18:18">
+      <c r="R894" s="1"/>
+    </row>
+    <row r="895" spans="18:18">
+      <c r="R895" s="1"/>
+    </row>
+    <row r="896" spans="18:18">
+      <c r="R896" s="1"/>
+    </row>
+    <row r="897" spans="18:18">
+      <c r="R897" s="1"/>
+    </row>
+    <row r="898" spans="18:18">
+      <c r="R898" s="1"/>
+    </row>
+    <row r="899" spans="18:18">
+      <c r="R899" s="1"/>
+    </row>
+    <row r="900" spans="18:18">
+      <c r="R900" s="1"/>
+    </row>
+    <row r="901" spans="18:18">
+      <c r="R901" s="1"/>
+    </row>
+    <row r="902" spans="18:18">
+      <c r="R902" s="1"/>
+    </row>
+    <row r="903" spans="18:18">
+      <c r="R903" s="1"/>
+    </row>
+    <row r="904" spans="18:18">
+      <c r="R904" s="1"/>
+    </row>
+    <row r="905" spans="18:18">
+      <c r="R905" s="1"/>
+    </row>
+    <row r="906" spans="18:18">
+      <c r="R906" s="1"/>
+    </row>
+    <row r="907" spans="18:18">
+      <c r="R907" s="1"/>
+    </row>
+    <row r="908" spans="18:18">
+      <c r="R908" s="1"/>
+    </row>
+    <row r="909" spans="18:18">
+      <c r="R909" s="1"/>
+    </row>
+    <row r="910" spans="18:18">
+      <c r="R910" s="1"/>
+    </row>
+    <row r="911" spans="18:18">
+      <c r="R911" s="1"/>
+    </row>
+    <row r="912" spans="18:18">
+      <c r="R912" s="1"/>
+    </row>
+    <row r="913" spans="18:18">
+      <c r="R913" s="1"/>
+    </row>
+    <row r="914" spans="18:18">
+      <c r="R914" s="1"/>
+    </row>
+    <row r="915" spans="18:18">
+      <c r="R915" s="1"/>
+    </row>
+    <row r="916" spans="18:18">
+      <c r="R916" s="1"/>
+    </row>
+    <row r="917" spans="18:18">
+      <c r="R917" s="1"/>
+    </row>
+    <row r="918" spans="18:18">
+      <c r="R918" s="1"/>
+    </row>
+    <row r="919" spans="18:18">
+      <c r="R919" s="1"/>
+    </row>
+    <row r="920" spans="18:18">
+      <c r="R920" s="1"/>
+    </row>
+    <row r="921" spans="18:18">
+      <c r="R921" s="1"/>
+    </row>
+    <row r="922" spans="18:18">
+      <c r="R922" s="1"/>
+    </row>
+    <row r="923" spans="18:18">
+      <c r="R923" s="1"/>
+    </row>
+    <row r="924" spans="18:18">
+      <c r="R924" s="1"/>
+    </row>
+    <row r="925" spans="18:18">
+      <c r="R925" s="1"/>
+    </row>
+    <row r="926" spans="18:18">
+      <c r="R926" s="1"/>
+    </row>
+    <row r="927" spans="18:18">
+      <c r="R927" s="1"/>
+    </row>
+    <row r="928" spans="18:18">
+      <c r="R928" s="1"/>
+    </row>
+    <row r="929" spans="18:18">
+      <c r="R929" s="1"/>
+    </row>
+    <row r="930" spans="18:18">
+      <c r="R930" s="1"/>
+    </row>
+    <row r="931" spans="18:18">
+      <c r="R931" s="1"/>
+    </row>
+    <row r="932" spans="18:18">
+      <c r="R932" s="1"/>
+    </row>
+    <row r="933" spans="18:18">
+      <c r="R933" s="1"/>
+    </row>
+    <row r="934" spans="18:18">
+      <c r="R934" s="1"/>
+    </row>
+    <row r="935" spans="18:18">
+      <c r="R935" s="1"/>
+    </row>
+    <row r="936" spans="18:18">
+      <c r="R936" s="1"/>
+    </row>
+    <row r="937" spans="18:18">
+      <c r="R937" s="1"/>
+    </row>
+    <row r="938" spans="18:18">
+      <c r="R938" s="1"/>
+    </row>
+    <row r="939" spans="18:18">
+      <c r="R939" s="1"/>
+    </row>
+    <row r="940" spans="18:18">
+      <c r="R940" s="1"/>
+    </row>
+    <row r="941" spans="18:18">
+      <c r="R941" s="1"/>
+    </row>
+    <row r="942" spans="18:18">
+      <c r="R942" s="1"/>
+    </row>
+    <row r="943" spans="18:18">
+      <c r="R943" s="1"/>
+    </row>
+    <row r="944" spans="18:18">
+      <c r="R944" s="1"/>
+    </row>
+    <row r="945" spans="18:18">
+      <c r="R945" s="1"/>
+    </row>
+    <row r="946" spans="18:18">
+      <c r="R946" s="1"/>
+    </row>
+    <row r="947" spans="18:18">
+      <c r="R947" s="1"/>
+    </row>
+    <row r="948" spans="18:18">
+      <c r="R948" s="1"/>
+    </row>
+    <row r="949" spans="18:18">
+      <c r="R949" s="1"/>
+    </row>
+    <row r="950" spans="18:18">
+      <c r="R950" s="1"/>
+    </row>
+    <row r="951" spans="18:18">
+      <c r="R951" s="1"/>
+    </row>
+    <row r="952" spans="18:18">
+      <c r="R952" s="1"/>
+    </row>
+    <row r="953" spans="18:18">
+      <c r="R953" s="1"/>
+    </row>
+    <row r="954" spans="18:18">
+      <c r="R954" s="1"/>
+    </row>
+    <row r="955" spans="18:18">
+      <c r="R955" s="1"/>
+    </row>
+    <row r="956" spans="18:18">
+      <c r="R956" s="1"/>
+    </row>
+    <row r="957" spans="18:18">
+      <c r="R957" s="1"/>
+    </row>
+    <row r="958" spans="18:18">
+      <c r="R958" s="1"/>
+    </row>
+    <row r="959" spans="18:18">
+      <c r="R959" s="1"/>
+    </row>
+    <row r="960" spans="18:18">
+      <c r="R960" s="1"/>
+    </row>
+    <row r="961" spans="18:18">
+      <c r="R961" s="1"/>
+    </row>
+    <row r="962" spans="18:18">
+      <c r="R962" s="1"/>
+    </row>
+    <row r="963" spans="18:18">
+      <c r="R963" s="1"/>
+    </row>
+    <row r="964" spans="18:18">
+      <c r="R964" s="1"/>
+    </row>
+    <row r="965" spans="18:18">
+      <c r="R965" s="1"/>
+    </row>
+    <row r="966" spans="18:18">
+      <c r="R966" s="1"/>
+    </row>
+    <row r="967" spans="18:18">
+      <c r="R967" s="1"/>
+    </row>
+    <row r="968" spans="18:18">
+      <c r="R968" s="1"/>
+    </row>
+    <row r="969" spans="18:18">
+      <c r="R969" s="1"/>
+    </row>
+    <row r="970" spans="18:18">
+      <c r="R970" s="1"/>
+    </row>
+    <row r="971" spans="18:18">
+      <c r="R971" s="1"/>
+    </row>
+    <row r="972" spans="18:18">
+      <c r="R972" s="1"/>
+    </row>
+    <row r="973" spans="18:18">
+      <c r="R973" s="1"/>
+    </row>
+    <row r="974" spans="18:18">
+      <c r="R974" s="1"/>
+    </row>
+    <row r="975" spans="18:18">
+      <c r="R975" s="1"/>
+    </row>
+    <row r="976" spans="18:18">
+      <c r="R976" s="1"/>
+    </row>
+    <row r="977" spans="18:18">
+      <c r="R977" s="1"/>
+    </row>
+    <row r="978" spans="18:18">
+      <c r="R978" s="1"/>
+    </row>
+    <row r="979" spans="18:18">
+      <c r="R979" s="1"/>
+    </row>
+    <row r="980" spans="18:18">
+      <c r="R980" s="1"/>
+    </row>
+    <row r="981" spans="18:18">
+      <c r="R981" s="1"/>
+    </row>
+    <row r="982" spans="18:18">
+      <c r="R982" s="1"/>
+    </row>
+    <row r="983" spans="18:18">
+      <c r="R983" s="1"/>
+    </row>
+    <row r="984" spans="18:18">
+      <c r="R984" s="1"/>
+    </row>
+    <row r="985" spans="18:18">
+      <c r="R985" s="1"/>
+    </row>
+    <row r="986" spans="18:18">
+      <c r="R986" s="1"/>
+    </row>
+    <row r="987" spans="18:18">
+      <c r="R987" s="1"/>
+    </row>
+    <row r="988" spans="18:18">
+      <c r="R988" s="1"/>
+    </row>
+    <row r="989" spans="18:18">
+      <c r="R989" s="1"/>
+    </row>
+    <row r="990" spans="18:18">
+      <c r="R990" s="1"/>
+    </row>
+    <row r="991" spans="18:18">
+      <c r="R991" s="1"/>
+    </row>
+    <row r="992" spans="18:18">
+      <c r="R992" s="1"/>
+    </row>
+    <row r="993" spans="18:18">
+      <c r="R993" s="1"/>
+    </row>
+    <row r="994" spans="18:18">
+      <c r="R994" s="1"/>
+    </row>
+    <row r="995" spans="18:18">
+      <c r="R995" s="1"/>
+    </row>
+    <row r="996" spans="18:18">
+      <c r="R996" s="1"/>
+    </row>
+    <row r="997" spans="18:18">
+      <c r="R997" s="1"/>
+    </row>
+    <row r="998" spans="18:18">
+      <c r="R998" s="1"/>
+    </row>
+    <row r="999" spans="18:18">
+      <c r="R999" s="1"/>
+    </row>
+    <row r="1000" spans="18:18">
+      <c r="R1000" s="1"/>
+    </row>
+    <row r="1001" spans="18:18">
+      <c r="R1001" s="1"/>
+    </row>
+    <row r="1002" spans="18:18">
+      <c r="R1002" s="1"/>
+    </row>
+    <row r="1003" spans="18:18">
+      <c r="R1003" s="1"/>
+    </row>
+    <row r="1004" spans="18:18">
+      <c r="R1004" s="1"/>
+    </row>
+    <row r="1005" spans="18:18">
+      <c r="R1005" s="1"/>
+    </row>
+    <row r="1006" spans="18:18">
+      <c r="R1006" s="1"/>
+    </row>
+    <row r="1007" spans="18:18">
+      <c r="R1007" s="1"/>
+    </row>
+    <row r="1008" spans="18:18">
+      <c r="R1008" s="1"/>
+    </row>
+    <row r="1009" spans="18:18">
+      <c r="R1009" s="1"/>
+    </row>
+    <row r="1010" spans="18:18">
+      <c r="R1010" s="1"/>
+    </row>
+    <row r="1011" spans="18:18">
+      <c r="R1011" s="1"/>
+    </row>
+    <row r="1012" spans="18:18">
+      <c r="R1012" s="1"/>
+    </row>
+    <row r="1013" spans="18:18">
+      <c r="R1013" s="1"/>
+    </row>
+    <row r="1014" spans="18:18">
+      <c r="R1014" s="1"/>
+    </row>
+    <row r="1015" spans="18:18">
+      <c r="R1015" s="1"/>
+    </row>
+    <row r="1016" spans="18:18">
+      <c r="R1016" s="1"/>
+    </row>
+    <row r="1017" spans="18:18">
+      <c r="R1017" s="1"/>
+    </row>
+    <row r="1018" spans="18:18">
+      <c r="R1018" s="1"/>
+    </row>
+    <row r="1019" spans="18:18">
+      <c r="R1019" s="1"/>
+    </row>
+    <row r="1020" spans="18:18">
+      <c r="R1020" s="1"/>
+    </row>
+    <row r="1021" spans="18:18">
+      <c r="R1021" s="1"/>
+    </row>
+    <row r="1022" spans="18:18">
+      <c r="R1022" s="1"/>
+    </row>
+    <row r="1023" spans="18:18">
+      <c r="R1023" s="1"/>
+    </row>
+    <row r="1024" spans="18:18">
+      <c r="R1024" s="1"/>
+    </row>
+    <row r="1025" spans="18:18">
+      <c r="R1025" s="1"/>
+    </row>
+    <row r="1026" spans="18:18">
+      <c r="R1026" s="1"/>
+    </row>
+    <row r="1027" spans="18:18">
+      <c r="R1027" s="1"/>
+    </row>
+    <row r="1028" spans="18:18">
+      <c r="R1028" s="1"/>
+    </row>
+    <row r="1029" spans="18:18">
+      <c r="R1029" s="1"/>
+    </row>
+    <row r="1030" spans="18:18">
+      <c r="R1030" s="1"/>
+    </row>
+    <row r="1031" spans="18:18">
+      <c r="R1031" s="1"/>
+    </row>
+    <row r="1032" spans="18:18">
+      <c r="R1032" s="1"/>
+    </row>
+    <row r="1033" spans="18:18">
+      <c r="R1033" s="1"/>
+    </row>
+    <row r="1034" spans="18:18">
+      <c r="R1034" s="1"/>
+    </row>
+    <row r="1035" spans="18:18">
+      <c r="R1035" s="1"/>
+    </row>
+    <row r="1036" spans="18:18">
+      <c r="R1036" s="1"/>
+    </row>
+    <row r="1037" spans="18:18">
+      <c r="R1037" s="1"/>
+    </row>
+    <row r="1038" spans="18:18">
+      <c r="R1038" s="1"/>
+    </row>
+    <row r="1039" spans="18:18">
+      <c r="R1039" s="1"/>
+    </row>
+    <row r="1040" spans="18:18">
+      <c r="R1040" s="1"/>
+    </row>
+    <row r="1041" spans="18:18">
+      <c r="R1041" s="1"/>
+    </row>
   </sheetData>
-  <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="A2:A1048576">
+  <dataValidations count="16">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="温馨提示" error="该单元格只能选下拉框中的数据!" sqref="E2:E1041">
+      <formula1>CHB_INVEST_TRADE_ENUM!$A$3:$L$3</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="温馨提示" error="该单元格只能选下拉框中的数据!" sqref="A2:A1041">
       <formula1>"导出,新增,修改,删除"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="E2:E1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1042:H1048576">
+      <formula1>CHB_INVEST_TRADE_ENUM!$A$5:$B$5</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="A1042:A1048576">
+      <formula1>"导出,新增,修改,删除"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="温馨提示" error="该单元格只能选下拉框中的数据!" sqref="I2:I1041">
+      <formula1>CHB_INVEST_TRADE_ENUM!$A$7:$FV$7</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="温馨提示" error="该单元格只能选下拉框中的数据!" sqref="H2:H1041">
+      <formula1>CHB_INVEST_TRADE_ENUM!$A$5:$B$5</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="E1042:E1048576">
       <formula1>CHB_INVEST_TRADE_ENUM!$A$3:$L$3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H1048576">
-      <formula1>CHB_INVEST_TRADE_ENUM!$A$5:$B$5</formula1>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="温馨提示" error="该单元格只能输入整数！" sqref="G2:G1041">
+      <formula1>-9.99999999999999E+29</formula1>
+      <formula2>9.99999999999999E+29</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="温馨提示" error="该单元格只能输入数字!" sqref="L2:L1041">
+      <formula1>-9.99999999999999E+29</formula1>
+      <formula2>9.99999999999999E+29</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I1042:I1048576">
       <formula1>CHB_INVEST_TRADE_ENUM!$A$7:$FV$7</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="温馨提示" error="该单元格只能输入数字!&#10;" sqref="J2:J1041 K2:K1041">
+      <formula1>-9.99999999999999E+29</formula1>
+      <formula2>9.99999999999999E+29</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="温馨提示" sqref="M2:M1041">
+      <formula1>-9.99999999999999E+29</formula1>
+      <formula2>9.99999999999999E+29</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="温馨提示" error="该单元格只能输入数字!" sqref="N2:N1041">
+      <formula1>-999999</formula1>
+      <formula2>999999</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="温馨提示" error="该单元格只能选下拉框中的数据！" sqref="P2:P1041">
       <formula1>"01 住户,02 广义政府,03 非金融企业,04 银行业存款类金融机构,05 银行非存款类金融机构,06 非银行业金融机构,07银行非保本理财,08 信托公司资管产品,09 证券公司及其子公司资管产品,10 基金管理公司及其子公司专户,11 期货公司及其子公司资管产品,12 保险资管产品,13 金融资产投资公司资管产品,14 公募基金,15 私募基金,16 其他特定目的载体,17 境外,99 其他"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P1042:P1048576">
+      <formula1>"01 住户,02 广义政府,03 非金融企业,04 银行业存款类金融机构,05 银行非存款类金融机构,06 非银行业金融机构,07银行非保本理财,08 信托公司资管产品,09 证券公司及其子公司资管产品,10 基金管理公司及其子公司专户,11 期货公司及其子公司资管产品,12 保险资管产品,13 金融资产投资公司资管产品,14 公募基金,15 私募基金,16 其他特定目的载体,17 境外,99 其他"</formula1>
+    </dataValidation>
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="温馨提示" error="正确格式为1900-01-01或1900/1/1，&#10;且取值范围为1900/1/1到9999/12/31!&#10;" sqref="R2:R1041">
+      <formula1>1</formula1>
+      <formula2>2958465</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/InvestmentDealInfo.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/InvestmentDealInfo.xlsx
@@ -655,11 +655,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -678,13 +678,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
@@ -692,7 +685,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -706,6 +699,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
@@ -713,9 +714,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -736,25 +743,48 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -769,15 +799,7 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -787,28 +809,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -830,13 +830,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -848,7 +842,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -866,7 +860,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -878,19 +902,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -902,19 +914,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -932,13 +932,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -950,31 +968,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -986,31 +998,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1021,6 +1021,21 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1035,6 +1050,15 @@
       </top>
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1054,17 +1078,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1088,15 +1106,6 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
@@ -1112,15 +1121,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1129,10 +1129,10 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1141,133 +1141,133 @@
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -4799,6 +4799,9 @@
     </row>
   </sheetData>
   <dataValidations count="16">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="温馨提示" error="该单元格只能选下拉框中的数据！" sqref="P2:P1042">
+      <formula1>"01 住户,02 广义政府,03 非金融企业,04 银行业存款类金融机构,05 银行非存款类金融机构,06 非银行业金融机构,07 银行非保本理财,08 信托公司资管产品,09 证券公司及其子公司资管产品,10 基金管理公司及其子公司专户,11 期货公司及其子公司资管产品,12 保险资管产品,13 金融资产投资公司资管产品,14 公募基金,15 私募基金,16 其他特定目的载体,17 境外,99 其他"</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="温馨提示" error="该单元格只能选下拉框中的数据!" sqref="E2:E1041">
       <formula1>CHB_INVEST_TRADE_ENUM!$A$3:$L$3</formula1>
     </dataValidation>
@@ -4843,10 +4846,7 @@
       <formula1>-999999</formula1>
       <formula2>999999</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="温馨提示" error="该单元格只能选下拉框中的数据！" sqref="P2:P1041">
-      <formula1>"01 住户,02 广义政府,03 非金融企业,04 银行业存款类金融机构,05 银行非存款类金融机构,06 非银行业金融机构,07银行非保本理财,08 信托公司资管产品,09 证券公司及其子公司资管产品,10 基金管理公司及其子公司专户,11 期货公司及其子公司资管产品,12 保险资管产品,13 金融资产投资公司资管产品,14 公募基金,15 私募基金,16 其他特定目的载体,17 境外,99 其他"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P1042:P1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P1043:P1048576">
       <formula1>"01 住户,02 广义政府,03 非金融企业,04 银行业存款类金融机构,05 银行非存款类金融机构,06 非银行业金融机构,07银行非保本理财,08 信托公司资管产品,09 证券公司及其子公司资管产品,10 基金管理公司及其子公司专户,11 期货公司及其子公司资管产品,12 保险资管产品,13 金融资产投资公司资管产品,14 公募基金,15 私募基金,16 其他特定目的载体,17 境外,99 其他"</formula1>
     </dataValidation>
     <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="温馨提示" error="正确格式为1900-01-01或1900/1/1，&#10;且取值范围为1900/1/1到9999/12/31!&#10;" sqref="R2:R1041">
